--- a/output/2026-10_품목신고보고현황.xlsx
+++ b/output/2026-10_품목신고보고현황.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="47" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
@@ -1998,150 +1998,209 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>2020001150810</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>프리미엄 골드 비타민C 3000</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>주식회사 한성헬시온</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>(1) 결합조직 형성과 기능유지에 필요
+(2) 철의 흡수에 필요
+(3) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 직접 또는 물에 녹여 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>비타민C</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>200400150832596</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>캡슐</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>일동 닥터파인 Fine</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>주식회사한미양행</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>[비타민E]
 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>제조일로부터 24개월까지</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>1일 2회, 1회 1캡슐을 충분한 물과 함께 섭취.</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>d-α-토코페롤, 글리세린지방산에스테르, 프탈산히드록시프로필메틸셀룰로스, D-소비톨액, 글리세린, 젤라틴, 비타민D3혼합제제, 오렌지향혼합제제, 합성향료(d-Limonene), 소나무잎유</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>비타민</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20040015104484</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>분말</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MOMSTAMIN 2'-FL PRE&amp;PROBIOTICS Premium(전량수출용)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>주식회사 네추럴웨이</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>유산균 증식 및 유해균 억제 · 배변활동 원활 · 장 건강에 도움을 줄 수 있음</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>제조일로부터 24개월</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1일 1회, 1회 1포를 직접 또는 충분한 물과 함께 섭취하십시오.</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>프로바이오틱스(고시형), 프로바이오틱스(고시형), 전지분유, 혼합제제, 이산화규소, 비타민C, 구연산(무수), 산화아연, 비타민D3혼합제제, 자일리톨, 이소말트, 당류가공품, 요거트혼합분말</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>프로바이오틱스</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>20040015104484</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MOMSTAMIN 2'-FL PRE&amp;PROBIOTICS Premium(전량수출용)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>주식회사 네추럴웨이</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>유산균 증식 및 유해균 억제 · 배변활동 원활 · 장 건강에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 직접 또는 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>프로바이오틱스(고시형), 프로바이오틱스(고시형), 전지분유, 혼합제제, 이산화규소, 비타민C, 구연산(무수), 산화아연, 비타민D3혼합제제, 자일리톨, 이소말트, 당류가공품, 요거트혼합분말</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>200400150832597</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>정</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>쑥쑥튼튼 키즈 철분&amp;비타민C 츄어블</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>주식회사한미양행</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>[비타민C]
 (가) 결합조직 형성과 기능유지에 필요
@@ -2152,116 +2211,116 @@
 (나) 에너지 생성에 필요</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>제조일로부터 24개월까지</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>1일 2회, 1회 1정을 씹어서 섭취.</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>비타민C, 피로인산제이철, 초유분말, 블루베리농축분말, 포도당, 자일리톨, 치커리뿌리추출물분말, 전지분유, 블루베리향분말, 이산화규소, 스테아린산마그네슘, 쌀발효분말, 효소처리스테비아, 과일채소혼합분말</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>비타민</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2023002721167</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>분말</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>락티카제이바실러스 람노서스 352 4,000억</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>위바이옴 익산공장</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>유산균 증식 및 유해균 억제·배변활동 원활·장 건강에 도움을 줄 수 있음</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>제조일로부터 18개월까지</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>식품 및 건강기능식품 제조 시 일일 섭취량에 적합한 양을 사용</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>프로바이오틱스(고시형), 건조옥수수전분</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>프로바이오틱스</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>2023002721167</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>락티카제이바실러스 람노서스 352 4,000억</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>위바이옴 익산공장</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>유산균 증식 및 유해균 억제·배변활동 원활·장 건강에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월까지</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>식품 및 건강기능식품 제조 시 일일 섭취량에 적합한 양을 사용</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>프로바이오틱스(고시형), 건조옥수수전분</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>20172880236472</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>분말</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>비타C 3000 맥스 플러스</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>주식회사 코스팜</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>[비타민C]
 1) 결합조직 형성과 기능유지에 필요
@@ -2271,59 +2330,59 @@
 1) 체내 에너지 생성에 필요</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>제조일로부터 24개월</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>1일 1회, 1회 1포를 200 ml의 물에 타서 섭취하십시오.</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>비타민 C(고시형), 비타민 B2(고시형), 에리스리톨, 탄산수소나트륨, 레몬과즙분말, 프락토올리고당(고시형), DL-사과산, 녹차발효추출액, 레몬향, 구연산(무수), 이산화규소, 효소처리스테비아, 오렌지농축분말, 자몽농축분말, 유자과즙분말, 수크랄로스</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>비타민</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>20040015094284</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>액상</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>저분자 모발콜라겐 펩타이드 비오틴 액상 헤어콜라겐 플러스+</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>(주)화인내츄럴</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>(국문) ① 피부 보습에 도움을 줄 수 있음
           ② 자외선에 의한 피부 손상으로부터 피부 건강을 유지하는데 도움을 줄 수 있음
@@ -2337,83 +2396,2350 @@
 (1) 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>제조일로부터 24개월</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>1일 1회, 1회 1포를 섭취하십시오.</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>비오틴, 아셀렌산나트륨, 황산망간, 글루콘산아연, 저분자콜라겐펩타이드(제2023-33호), 가다랑어 엘라스틴 펩타이드(VGPG Elastin®)(제2022-38호), 구연산삼나트륨, 판토텐산칼슘, 엘라스틴가수분해물, 황금추출물, 비타민C, 혼합제제, 잔탄검, 효소처리스테비아, 레몬향, 사과향, 사과농축분말, 사과농축액, 시클로덱스트린, 레몬농축액, 에리스리톨, 알룰로오스, 정제수, 혼합제제, 유함유가공품</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>이너뷰티</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2020001150810</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>200400150832599</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>비타민B12</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>주식회사한미양행</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>[비타민B12]
+정상적인 엽산 대사에 필요</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 충분한 물과 함께 섭취.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>비타민B12혼합제제분말, 캡슐류, 이산화규소, 스테아린산마그네슘, 유당분말</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20210016229146</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>알레스카 알티지 오메가3</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>엔피케이(주) 2공장</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>[EPA 및 DHA 함유 유지]혈중 중성지질 개선･혈행 개선･기억력 개선･건조한 눈을 개선하여 눈 건강에 도움을 줄 수 있음
+[비타민D]①칼슘과 인이 흡수되고 이용되는데 필요②뼈의 형성과 유지에 필요③골다공증발생 위험감소에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>제조일로부터 36개월</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>EPA및DHA함유유지(고시형), 비타민D3혼합제제, 젤라틴, 글리세린, D-소비톨액, 콩기름(대두유)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>오메가3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>200600200081483</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>웰라이프 루테인지아잔틴 플러스</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스2공장</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>[마리골드꽃추출물(지아잔틴함유)(제2026-9호)] 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음
+[비타민 C] 결합조직 형성과 기능유지에 필요, 철의 흡수에 필요, 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[비타민 E] 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[아연] 정상적인 면역기능에 필요, 정상적인 세포분열에 필요
+[비타민 B12] 정상적인 엽산 대사에 필요
+[비타민 A] 어두운 곳에서 시각 적응을 위해 필요, 피부와 점막을 형성하고 기능을 유지하는데 필요, 상피세포의 성장과 발달에 필요
+[비타민 B6] 단백질 및 아미노산 이용에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민 B2] 체내 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>비타민 B2(고시형), 비타민 B6(고시형), 비타민 A(고시형), 비타민 C(고시형), 비타민 E(고시형), 산화아연(고시형), 비타민 B12(고시형), 마리골드꽃추출물(지아잔틴함유)(제2026-9호), 안나토색소, 덱스트린, 카라기난, 글리세린, 변성전분, 정제수, 레시틴, 밀납(백납), 콩기름(대두유)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>201000190041599</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>분말</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>프리미엄 비타민C 3000 골드</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>주식회사 한성헬시온</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>(1) 결합조직 형성과 기능유지에 필요
-(2) 철의 흡수에 필요
-(3) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>몬스터 크레아틴 부스터</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>엔피케이(주)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>[크레아틴] 근력 운동 시에 운동수행능력 향상에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>제조일부터 24 개월</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1스푼(3.6g)을 직접 또는 기호 음료에 희석하여 섭취</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>크레아틴(고시형), 혼합제제, L-로이신, 베타인, 타우린, L-글루타민, 대나무수액, 덱스트린, 판토텐산칼슘, 니코틴산아미드, 비오틴, L-카르니틴</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>200600200081485</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>아이원 루테인지아잔틴 포스파티딜세린 PS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스2공장</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>[포스파티딜세린] 노화로 인해 저하된 인지력 개선·자외선에 의한 피부 손상으로부터 피부 건강 유지·피부보습에 도움을 줄 수 있음
+[루테인지아잔틴추출복합물(제2025-35호)]
+(국문) 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음
+(영문) May support eye health by maintaining the density of macular pigments which can be affected by aging</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2캡슐(1캡슐당 700mg)을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>포스파티딜세린(고시형), 루테인지아잔틴추출복합물(제2025-35호), 카카오색소, 덱스트린, 카라기난, 글리세린, 변성전분, 정제수, 잇꽃씨앗유</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20172880236474</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>나이아가라 쏘팔메토</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>주식회사 코스팜</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>[쏘팔메토 열매 추출물]
+1) 전립선 건강의 유지에 도움을 줄 수 있음
+[옥타코사놀 함유 유지]
+1) 지구력 증진에 도움을 줄 수 있음
+[아연]
+1) 정상적인 면역기능에 필요
+2) 정상적인 세포분열에 필요
+[비타민B2]
+1) 체내 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>쏘팔메토 열매 추출물(고시형), 옥타코사놀 함유 유지(고시형), 산화아연(고시형), 비타민 B2(고시형), 에틸바닐린, 카카오색소, 젤라틴, 글리세린, D-소비톨액, 포도씨앗유, 밀납(백납), 비수리추출분말, 마카뿌리분말, L-아르지닌, 산수유추출분말, 토마토농축분말, 황산망간</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>남성건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>200600200081484</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>아이원 루테인지아잔틴 플러스 징코</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스2공장</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>[루테인지아잔틴추출복합물(제2025-35호)]
+(국문) 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음
+(영문) May support eye health by maintaining the density of macular pigments which can be affected by aging
+[은행잎 추출물] 기억력 개선·혈행 개선에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>은행잎추출물(고시형), 루테인지아잔틴추출복합물(제2025-35호), 카카오색소, 덱스트린, 카라기난, 글리세린, 변성전분, 정제수, 레시틴, 밀납(백납), 잇꽃씨앗유</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>200400200083490</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>마그네슘05 플러스 비타민B12</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>[마그네슘] 에너지 이용에 필요, 신경과 근육 기능 유지에 필요
+[셀레늄] 유해산소로부터 세포를 보호하는데 필요
+[비타민 B6] 단백질 및 아미노산 이용에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민 B1] 탄수화물과 에너지 대사에 필요
+[비타민 B2] 체내 에너지 생성에 필요
+[비타민 B12] 정상적인 엽산 대사에 필요</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>산화마그네슘(고시형), 스테아린산마그네슘(고시형), 아셀렌산나트륨(고시형), 비타민 B6(고시형), 비타민 B1(고시형), 비타민 B2(고시형), 비타민 B12(고시형), 결정셀룰로스, 덱스트린, 히드록시프로필메틸셀룰로스, 가교카복시메틸셀룰로스나트륨, 이산화티타늄, 글리세린지방산에스테르혼합제제용액, 과일채소혼합농축액</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20040020041578</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>환</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>쾌변루틴 차전자피 식이섬유 환</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>노비스바이오(주)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>[차전자피식이섬유] 배변활동 원활에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1일 2회, 1회 1포(3.2g)을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>차전자피식이섬유(고시형), 기타가공품, 고형차, 과.채가공품, 과.채가공품, 식품첨가물, 기타가공품</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>장</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20160006007147</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>싱글맥스 프로바이오틱스50+</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>(주)종근당바이오</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>유산균 증식 및 유해균 억제･배변활동 원활･장 건강에 도움을 줄 수 있음
+(1) 정상적인 면역기능에 필요
+(2) 정상적인 세포분열에 필요
+(1) 칼슘과 인이 흡수되고 이용되는데 필요
+(2) 뼈의 형성과 유지에 필요
+(3) 골다공증발생 위험 감소에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Bifidobacterium animalis ssp. lactis(고시형), Lactiplantibacillus plantarum(고시형), Lacticaseibacillus casei(고시형), Bifidobacterium longum(고시형), Lacticaseibacillus rhamnosus(고시형), Lactobacillus acidophilus(고시형), Streptococcus thermophilus(고시형), 산화아연, 비타민D3혼합제제, 구연산, 복숭아향분말, 자일리톨혼합제제, 복사나무열매과즙분말, 포도당, 덱스트린, 자일로올리고당, 프락토올리고당, 에리스리톨, 식물성크림혼합분말, 갈락토올리고당, 귀리식이섬유, 덱스트린</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20172880193516</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>액상</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>모발콜라겐3X샷</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>대원헬스케어 주식회사 2공장</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>[저분자콜라겐펩타이드(제2023-33호)]
+(국문) ① 피부 보습에 도움을 줄 수 있음
+         ② 자외선에 의한 피부 손상으로부터 피부 건강을 유지하는데 도움을 줄 수 있음
+         ③ 모발상태(윤기·탄력) 개선에 도움을 줄 수 있음 
+(영문) ① May help to maintain skin moisturizing
+         ② May help to maintain skin health from skin damage by UV radiation
+         ③ May help to improve hair condition(luster·elasticity)
+[비오틴]
+(1) 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>제조일로부터 24개월까지</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1일 1회, 1회 1포를 직접 또는 물에 녹여 섭취하십시오.</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>비타민C</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 흔들어 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>비오틴(고시형), 저분자콜라겐펩타이드(제2023-33호), 가다랑어 엘라스틴 펩타이드(VGPG Elastin®)(제2022-38호), 효소처리스테비아, DL-사과산, γ-시클로덱스트린, 구연산(무수), 사과향, 자일리톨, 사과농축액, 프락토올리고당, 정제수, 글루콘산아연, 구연산삼나트륨, 레몬향, 아미노산혼합분말, 아셀렌산나트륨, 판토텐산칼슘, 우유단백질, 황금추출물, 엘라스틴가수분해물, 잔탄검, 사과추출물분말, 히알루론산</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>이너뷰티</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>200700170353315</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Bloomage Health Easy Move Tablets (전량수출용)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티(주)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>[비타민 D]
+칼슘과 인이 흡수되고 이용되는데 필요
+뼈의 형성과 유지에 필요
+골다공증발생 위험 감소에 도움을 줌
+[비타민 B1]
+탄수화물과 에너지 대사에 필요</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2정을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>비타민B1질산염, 비타민D3혼합제제, 보스웰리아검레진, 결정셀룰로스, NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 가교카복시메틸셀룰로스나트륨, 히알루론산(고시형), 히드록시프로필메틸셀룰로스, 이산화규소, 이산화티타늄, 글리세린, 스테아린산마그네슘</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>뼈건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20040015104485</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>그린몬스터 크레아틴 모노하이드레이트</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>주식회사 네추럴웨이</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>[크레아틴] 근력 운동 시에 운동수행능력 향상에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1일 1회, 3g을 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>크레아틴(고시형)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>200600200081480</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>아이원 루테인지아잔틴 혈당관리 바나바잎</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스2공장</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>[루테인지아잔틴추출복합물(제2025-35호)]
+(국문) 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음
+(영문) May support eye health by maintaining the density of macular pigments which can be affected by aging
+[바나바잎 추출물] 식후 혈당상승 억제에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>바나바잎 추출물(고시형), 루테인지아잔틴추출복합물(제2025-35호), 카카오색소, 덱스트린, 카라기난, 글리세린, 변성전분, 정제수, 레시틴, 밀납(백납), 잇꽃씨앗유</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20040015094285</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>액상</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>마시는 활력 마그네슘 영양제 250</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>(주)화인내츄럴</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>(1) 에너지 이용에 필요
+(2) 신경과 근육 기능 유지에 필요
+(1) 탄수화물과 에너지 대사에 필요
+(1) 체내 에너지 생성에 필요
+(1) 단백질 및 아미노산 이용에 필요
+(2) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+(1) 정상적인 면역기능에 필요
+(2) 정상적인 세포분열에 필요</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1병를 그대로 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>비타민B2, 비타민B6염산염, 비타민B1염산염, 글루콘산아연, L-젖산마그네슘, 황금추출물, 기타가공품, 동결건조로얄젤리분말, 녹용발효추출분말, 효소식품, 구연산삼나트륨, 효소처리스테비아, 구연산(무수), 사과향, 요구르트향, DL-사과산, 에리스리톨, 알룰로오스, 정제수, 수크랄로스, 난백분, 혼합제제, 식물혼합추출물분말</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20240028080624</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>더 파르마 굿모닝 &amp; 굿이브닝</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>콜마비앤에이치(주)세종3공장</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>- 아쉬아간다 추출물(KSM-66®)(제2025-67호) : 스트레스로 인한 긴장완화에 도움을 줄 수 있음 
+- 비타민 B1 : 탄수화물과 에너지 대사에 필요
+- 비타민 B6 : 단백질 및 아미노산 이용에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+- 비타민 B12 : 정상적인 엽산 대사에 필요 
+- 나이아신 : 체내 에너지 생성에 필요
+- 판토텐산 : 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+- 셀레늄(또는 셀렌) : 유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1일 2회, 오전에 1정(흰색), 오후에 1정(보라색)을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>비타민 B12(고시형), 비타민B6염산염, 비타민B1염산염, 판토텐산칼슘(고시형), 건조효모(셀렌함유), 니코틴산아미드(고시형), 아쉬아간다추출물(KSM-66®)(제2025-67호), 치자적색소, 스피어민트향분말, 이산화티타늄, 스테아린산마그네슘, 이산화규소, 가교카복시메틸셀룰로스나트륨, 히드록시프로필메틸셀룰로스, 덱스트린, 토마토추출물분말, 해조칼슘, 덱스트린, 결정셀룰로스, 글리세린지방산에스테르, 치자청색소</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20040015094286</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>리얼업 뼈건강엔 칼마디K2플러스 칼슘 마그네슘 아연 비타민D 비타민K2 망간</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>(주)화인내츄럴</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>(1) 뼈와 치아 형성에 필요
+(2) 신경과 근육 기능 유지에 필요
+(3) 정상적인 혈액응고에 필요
+(4) 골다공증발생 위험 감소에 도움을 줌
+(1) 에너지 이용에 필요
+(2) 신경과 근육 기능 유지에 필요
+(1) 칼슘과 인이 흡수되고 이용되는데 필요
+(2) 뼈의 형성과 유지에 필요
+(3) 골다공증발생 위험 감소에 도움을 줌
+(1) 정상적인 면역기능에 필요
+(2) 정상적인 세포분열에 필요
+(1) 정상적인 혈액응고에 필요
+(2) 뼈의 구성에 필요
+(1) 뼈 형성에 필요
+(2) 에너지 이용에 필요
+(3) 유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>황산망간, 비타민D3혼합제제, 산화아연, 비타민K2, 산화마그네슘, 꼬막, 엠에스엠(고시형), 이산화규소, 스테아린산마그네슘, 히드록시프로필메틸셀룰로스, 카복시메틸셀룰로스칼슘, 결정셀룰로스, 덱스트린, 비타민B1염산염, 상어연골추출물분말, 글리세린지방산에스테르, 유청칼슘, 건조효모, 야채혼합농축분말</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>뼈건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>200600200081479</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>파비플로라</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스2공장</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>[파비플로라생강뿌리추출물(제2024-14호)]
+(국문) 체지방 감소에 도움을 줄 수 있음
+(영문) May help to reduce body fat</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>파비플로라생강뿌리추출물(제2024-14호), 이산화티타늄, 젤라틴, 글리세린, D-소비톨액, 카카오색소, 안나토색소, 콩기름(대두유), 밀납(백납), 레시틴</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>다이어트</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>200700170353314</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DAILY WISE 혈당 바나바 맥스</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티(주)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>[비타민 D]
+칼슘과 인이 흡수되고 이용되는데 필요
+뼈의 형성과 유지에 필요
+골다공증발생 위험 감소에 도움을 줌
+[비타민 B1]
+탄수화물과 에너지 대사에 필요
+[비타민 B6]
+단백질 및 아미노산 이용에 필요
+혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[아연]
+정상적인 면역기능에 필요
+정상적인 세포분열에 필요
+[크롬]
+체내 탄수화물, 지방, 단백질 대사에 관여
+[바나바잎 추출물]
+식후 혈당상승 억제에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>바나바잎 추출물(고시형), 건조효모, 산화아연, 비타민B1질산염, 비타민B6염산염, 비타민D3혼합제제, 카나우바왁스, 글리세린, 히드록시프로필메틸셀룰로스, 스테아린산마그네슘, 카복시메틸셀룰로스칼슘, 덱스트린, 결정셀룰로스</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20190009483931</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>유한 리포좀 비타민 C</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>우리바이오(주)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>[비타민 C]
+(가) 결합조직 형성과 기능유지에 필요
+(나) 철의 흡수에 필요
+(다) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>혼합제제, 결정셀룰로스, 덱스트린, 스테아린산, 히드록시프로필메틸셀룰로스, 히드록시프로필셀룰로스, 스테아린산마그네슘, 이산화규소, 가교카복시메틸셀룰로스나트륨, 이산화티타늄, 치자황색소, 글리세린지방산에스테르</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20172880236470</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>리포좀 멀티비타민&amp;미네랄 골드 17</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>주식회사 코스팜</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>[비타민C]
+1) 결합조직 형성과 기능유지에 필요
+2) 철의 흡수에 필요
+3) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[비타민E]
+1) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[나이아신]
+1) 체내 에너지 생성에 필요
+[몰리브덴]
+1) 산화･환원 효소의 활성에 필요
+[아연]
+1) 정상적인 면역기능에 필요
+2) 정상적인 세포분열에 필요
+[망간]
+1) 뼈 형성에 필요
+2) 에너지 이용에 필요
+3) 유해산소로부터 세포를 보호하는데 필요
+[비타민A]
+1) 어두운 곳에서 시각 적응을 위해 필요
+2) 피부와 점막을 형성하고 기능을 유지하는데 필요
+3) 상피세포의 성장과 발달에 필요
+[판토텐산]
+1) 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+[비타민D]
+1) 칼슘과 인이 흡수되고 이용되는데 필요
+2) 뼈의 형성과 유지에 필요
+3) 골다공증 발생 위험 감소에 도움을 줌
+[비오틴]
+1) 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+[비타민B12]
+1) 정상적인 엽산 대사에 필요
+[구리]
+1) 철의 운반과 이용에 필요
+2) 유해산소로부터 세포를 보호하는데 필요
+[비타민B6]
+1) 단백질 및 아미노산 이용에 필요
+2) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민B1]
+1) 탄수화물과 에너지 대사에 필요
+[비타민B2]
+1) 체내 에너지 생성에 필요
+[엽산]
+1) 세포와 혈액생성에 필요
+2) 태아 신경관의 정상 발달에 필요
+3) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[철]
+1) 체내 산소운반과 혈액생성에 필요
+2) 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>철(고시형), 혼합제제, 결정셀룰로스, 이소말트, 가교카복시메틸셀룰로스나트륨, 카복시메틸셀룰로스칼슘, 이산화규소, 스테아린산마그네슘, 히드록시프로필메틸셀룰로스</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>멀티팩</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>200400150832600</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>치아튼튼 인사케어 플러스</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>주식회사한미양행</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>[프로폴리스추출물]
+구강에서의 항균작용에 도움을 줄 수 있음
+[비타민D]
+(가) 칼슘과 인이 흡수되고 이용되는데 필요
+(나) 뼈의 형성과 유지에 필요
+(다) 골다공증 발생 위험 감소에 도움을 줌
+[비타민C]
+(가) 결합조직 형성과 기능유지에 필요
+(나) 철의 흡수에 필요
+(다) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[칼슘]
+(가) 뼈와 치아 형성에 필요
+(나) 신경과 근육 기능 유지에 필요
+(다) 정상적인 혈액응고에 필요
+(라) 골다공증 발생 위험 감소에 도움을 줌
+[아연]
+(가) 정상적인 면역기능에 필요
+(나) 정상적인 세포분열에 필요
+[셀레늄]
+유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 씹어서 섭취.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>비타민D3혼합제제, 프로폴리스추출물(고시형), 탄산칼슘, 유청칼슘, 비타민C, 산화아연, 아셀렌산나트륨, 결정셀룰로스, 포도당, 식물성크림, 수크랄로스, l-멘톨, 효소처리스테비아, 스테아린산마그네슘, 이산화규소, 페퍼민트향, 히드록시프로필메틸셀룰로스</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>200600200033306</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>루잔틴3</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>콜마비앤에이치(주)음성공장</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>- 마리골드꽃추출물 : 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음
+- 헤마토코쿠스 추출물 : 눈의 피로도 개선에 도움을 줄 수 있음
+- 비타민 A : 어두운 곳에서 시각 적응을 위해 필요, 피부와 점막을 형성하고 기능을 유지하는데 필요, 상피세포의 성장과 발달에 필요
+- 비타민 E : 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>유성비타민A지방산에스테르, d-α-토코페롤, 마리골드꽃추출물(고시형), 헤마토코쿠스추출물(고시형), 변성전분, 글리세린, 카라기난, 덱스트린, D-소비톨액, EPA 및 DHA 함유 유지(고시형), 올리브유</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>200600200081482</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>코엔자임Q10 항산화&amp;비타민 미네랄 식물성캡슐</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스2공장</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>[코엔자임Q10] 항산화·높은 혈압 감소에 도움을 줄 수 있음
+[크롬] 체내 탄수화물, 지방, 단백질 대사에 관여
+[나이아신] 체내 에너지 생성에 필요
+[아연] 정상적인 면역기능에 필요, 정상적인 세포분열에 필요
+[판토텐산] 지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+[셀레늄] 유해산소로부터 세포를 보호하는데 필요
+[비타민B6] 단백질 및 아미노산 이용에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민B1] 탄수화물과 에너지 대사에 필요
+[비타민B2] 체내 에너지 생성에 필요
+[비타민D] 칼슘과 인이 흡수되고 이용되는데 필요, 뼈의 형성과 유지에 필요, 골다공증 발생 위험 감소에 도움을 줌
+[엽산] 세포와 혈액생성에 필요, 태아 신경관의 정상 발달에 필요, 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>엽산(고시형), 비타민 D3(고시형), 비타민 B2(고시형), 비타민 B1(고시형), 비타민 B6(고시형), 아셀렌산나트륨(고시형), 판토텐산칼슘(고시형), 산화아연(고시형), 니코틴산아미드(고시형), 크롬(고시형), 코엔자임Q10(고시형), 정제수, 변성전분, 글리세린, 카라기난, 덱스트린, 카카오색소, 콩기름(대두유), 밀납(백납), 레시틴</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>멀티팩</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20040017038327</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Herbalaid Phyto Flow(전량수출용)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>케이지랩 주식회사</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>[은행잎 추출물] 기억력 개선·혈행 개선에 도움을 줄 수 있음
+[코엔자임Q10] 항산화·높은 혈압 감소에 도움을 줄 수 있음
+[홍국] 혈중 콜레스테롤 개선에 도움을 줄 수 있음
+[바나바잎 추출물] 식후 혈당상승 억제에 도움을 줄 수 있음
+[아연] ①정상적인 면역기능에 필요②정상적인 세포분열에 필요</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1일 2회, 1회 1캡슐(1,100mg)을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>산화아연(고시형), 홍국분말(고시형), 바나바잎 추출물(고시형), 은행잎추출물(고시형), 코엔자임 Q10(고시형), 글리세린, 젤라틴, 이산화티타늄, 카라멜색소, 홍국색소, D-소비톨액, 고형차, 레시틴, 키토산(고시형), L-아르지닌, 꾸지뽕잎추출물, 과.채가공품, 밀납, 팜유, 콩기름(대두유)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024002023383</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>유한 코엔자임Q10</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>(주)비오팜2공장</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>[코엔자임Q10] (1)항산화･높은 혈압 감소에 도움을 줄 수 있음
+[나이아신] (1)체내 에너지 생성에 필요
+[판토텐산] (1)지방, 탄수화물, 단백질 대사와 에너지 생성에 필요
+[셀레늄(셀렌)] (1)유해산소로부터 세포를 보호하는데 필요
+[비타민E] (1)항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요
+[비타민B6] (1)단백질 및 아미노산 이용에 필요 (2) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민B1] (1)탄수화물과 에너지 대사에 필요
+[비타민B2] (1)체내 에너지 생성에 필요</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 충분한 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>비타민 B2(고시형), 비타민 B1염산염(고시형), 피리독신염산염(고시형), D-알파-토코페롤(고시형), 아셀렌산나트륨(고시형), 판토텐산칼슘(고시형), 니코틴산아미드(고시형), 코엔자임Q10(고시형), 카카오색소, D-소비톨액, 글리세린, 정제수, 젤라틴, 레시틴, 밀납, 콩기름(대두유)</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20160006007148</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>장건강엔 프로바이오틱스&amp;아연+</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>(주)종근당바이오</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>유산균 증식 및 유해균 억제･배변활동 원활･장 건강에 도움을 줄 수 있음
+(1) 정상적인 면역기능에 필요
+(2) 정상적인 세포분열에 필요
+(1) 칼슘과 인이 흡수되고 이용되는데 필요
+(2) 뼈의 형성과 유지에 필요
+(3) 골다공증발생 위험 감소에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Bifidobacterium longum(고시형), Lacticaseibacillus casei(고시형), Lactobacillus acidophilus(고시형), 유산균혼합분말, 산화아연, 비타민D3혼합제제, Bifidobacterium animalis ssp. lactis(고시형), Lactiplantibacillus plantarum(고시형), Streptococcus thermophilus(고시형), Lacticaseibacillus rhamnosus(고시형), 염화칼륨, 글리세린, 염화마그네슘, 소르비탄지방산에스테르, 카라기난, 이산화티타늄, 정제수, 히드록시프로필메틸셀룰로스, 유청칼슘, 포도당, 서양자두과즙분말, 치커리뿌리추출물, 프락토올리고당, 스테아린산마그네슘, 덱스트린, 결정셀룰로스</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>200600200081481</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>웰라이프 루테인지아잔틴 프로</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스2공장</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>[은행잎 추출물] 기억력 개선·혈행 개선에 도움을 줄 수 있음
+[루테인지아잔틴복합추출물(제2019-16호)]
+(국문) 노화로 인해 감소될 수 있는 황반색소밀도를 유지하여 눈 건강에 도움을 줄 수 있음, 건조한 눈을 개선하여 눈 건강에 도움을 줄 수 있음
+(영문) May help the eye health by maintaining the density of macular pigments which can be decreased by aging, May help to maintain eyes healthy by relieving dryness</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>은행잎추출물(고시형), 루테인지아잔틴복합추출물(제2019-16호), 안나토색소, 덱스트린, 카라기난, 글리세린, 변성전분, 정제수, 레시틴, 밀납(백납), 콩기름(대두유)</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>200400150832598</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>인지력 케어엔 포스파티딜세린 PS 300</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>주식회사한미양행</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>[포스파티딜세린]
+노화로 인해 저하된 인지력 개선･자외선에 의한 피부 손상으로부터 피부 건강 유지･피부보습에 도움을 줄 수 있음
+[비타민B6]
+(가) 단백질 및 아미노산 이용에 필요
+(나) 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[비타민B12]
+정상적인 엽산 대사에 필요</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월까지</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2정을 충분한 물과 함께 섭취.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>비타민B6염산염, 비타민B12혼합제제분말, 포스파티딜세린(고시형), 홍삼농축액(고시형), 은행잎추출물(고시형), 히드록시프로필메틸셀룰로스, 스테아린산마그네슘, 이산화규소, 폴리비닐피로리돈, 비타민C, 히드록시프로필셀룰로스, 가교카복시메틸셀룰로스나트륨, 해조칼슘, 유당분말, 결정셀룰로스, 산화마그네슘</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>두뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>200400200142208</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>더 화인골드 플러스(PLUS)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>광동헬스바이오(주) 2공장</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>[비타민E]
+(1) 항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2캡슐을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>D-알파-토코페롤(고시형), D-소비톨액, 덱스트린, 카라기난, 히드록시프로필전분, 글리세린, 정제수, 기타가공품</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20172880193517</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>액상</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>여에스더 젖산 마그네슘 트리플 샷</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>대원헬스케어 주식회사 2공장</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>[비타민B1] 탄수화물과 에너지 대사에 필요 
+[비타민B2] 체내 에너지 생성에 필요
+[비타민B6] 단백질 및 아미노산 이용에 필요 / 혈액의 호모시스테인 수준을 정상으로 유지하는데 필요
+[아연] 정상적인 면역기능에 필요 / 정상적인 세포분열에 필요 
+[마그네슘] 에너지 이용에 필요 / 신경과 근육 기능 유지에 필요</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월까지</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>젖산마그네슘(고시형), 글루콘산아연(고시형), 비타민 B1질산염(고시형), 비타민 B6(고시형), 비타민 B2(고시형), 정제수, 알룰로오스, 에리스리톨, β-시클로덱스트린, 구연산(무수), 청포도향, DL-사과산, 머스켓향, 효소처리스테비아, 잔탄검, 황금추출물, 수크랄로스, 아스파탐, Lactiplantibacillus plantarum, 판토텐산칼슘, 젖산칼슘, 타우린, 아미노산혼합분말</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>200700170353313</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>항산화 영국산 비타민C</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티(주)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>[비타민 C]
+결합조직 형성과 기능유지에 필요
+철의 흡수에 필요
+항산화 작용을 하여 유해산소로부터 세포를 보호하는데 필요</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1정을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>비타민C, 카나우바왁스, 글리세린, 히드록시프로필메틸셀룰로스, 이산화규소, 스테아린산마그네슘, 혼합제제, 결정셀룰로스</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>비타민</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2023002721170</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>락티플란티바실러스 플란타룸 396 2,000억</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>위바이옴 익산공장</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>유산균 증식 및 유해균 억제·배변활동 원활·장 건강에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월까지</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>식품 및 건강기능식품 제조 시 일일 섭취량에 적합한 양을 사용</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>프로바이오틱스(고시형), 건조옥수수전분</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2023002721169</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>리모시락토바실러스 퍼멘텀 375 1,000억</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>위바이옴 익산공장</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>유산균 증식 및 유해균 억제·배변활동 원활·장 건강에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>식품 및 건강기능식품 제조 시 일일 섭취량에 적합한 양을 사용</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>프로바이오틱스(고시형), 건조옥수수전분</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2023002721168</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>락티카제이바실러스 파라카제이 384 6,000억</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>위바이옴 익산공장</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>유산균 증식 및 유해균 억제·배변활동 원활·장 건강에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>제조일로부터 18개월</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>식품 및 건강기능식품 제조 시 일일 섭취량에 적합한 양을 사용</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>프로바이오틱스(고시형), 건조옥수수전분</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>200600200081486</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>캡슐</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>매일보궁 진</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스2공장</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>[크릴오일등복합물(FlexPro MD®)(제2022-39호)]
+(국문) 관절건강에 도움을 줄 수 있음
+(영문) May help to maintain healthy joint
+[은행잎 추출물] 기억력 개선·혈행 개선에 도움을 줄 수 있음</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 2캡슐(1캡슐당 600mg)을 물과 함께 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>은행잎추출물(고시형), 크릴오일등복합물(FlexPro MDⓇ)(제2022-39호), 글리세린, 젤라틴, D-소비톨액, 안나토색소, 비타민 D3(고시형), 뮤코다당.단백(고시형), 생선콜라겐, 보스웰리아추출물분말, 심황색소, 초록입홍합분말, 밀납(백납), 콩기름(대두유)</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>두뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20160006007146</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>락토 챔피언+</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>(주)종근당바이오</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>유산균 증식 및 유해균 억제･배변활동 원활･장 건강에 도움을 줄 수 있음
+(1) 칼슘과 인이 흡수되고 이용되는데 필요
+(2) 뼈의 형성과 유지에 필요
+(3) 골다공증발생 위험 감소에 도움을 줌
+(1) 정상적인 면역기능에 필요
+(2) 정상적인 세포분열에 필요</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>제조일로부터 24개월</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1일 1회, 1회 1포를 섭취하십시오.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Bifidobacterium animalis ssp. lactis(고시형), Lactiplantibacillus plantarum(고시형), Bifidobacterium longum(고시형), Lacticaseibacillus rhamnosus(고시형), Limosilactobacillus reuteri(고시형), 비타민D3혼합제제, 산화아연, Lactobacillus acidophilus(고시형), 자일리톨혼합제제, 요거트혼합분말, 덱스트린, 자일로올리고당, 유당, 블루베리농축분말, 포도당, 에리스리톨, 포도과즙분말, 프락토올리고당, 요구르트향분말, 블루베리향분말, 구연산, 비타민C, 유청칼슘, 귀리식이섬유</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>프로바이오틱스</t>
         </is>
       </c>
     </row>
@@ -2428,15 +4754,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
@@ -2492,7 +4818,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19930294014571</t>
+          <t>198604350131762</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2502,32 +4828,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19930294014</t>
+          <t>19860435013</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>프리미엄 가나 치즈&amp;티라미수</t>
+          <t>여에스더 하루 한 포 샐러드 포켓 젤리</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(주)대웅</t>
+          <t>코스맥스바이오(주)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>식물성크림, 기타코코아가공품, 과자, 코코아분말</t>
+          <t>정제수, 난소화성말토덱스트린(고시형), 난소화성말토덱스트린(고시형), 발효식초, 로커스트콩검, 치아씨앗, 사과향, 구연산, 구연산삼나트륨, 효소처리스테비아, 중쇄중성지방유, 사과농축액, 카라기난혼합제제, 과일채소혼합분말</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2539,7 +4865,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19990211056279</t>
+          <t>198604350131761</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2549,44 +4875,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19990211056</t>
+          <t>19860435013</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>핑크퐁 아이비타C+아연</t>
+          <t>EONER 그린파우더</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>다이식품 제2공장</t>
+          <t>코스맥스바이오(주)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>효소처리스테비아, 산화아연, 구연산, DL-사과산, 스테아린산마그네슘, 과.채가공품, 자일리톨, 비타민C, 포도당</t>
+          <t>비타민E혼합제제, 감자추출물분말, 건조효모, β-시클로덱스트린, 합성향료(4-Aminobutyric acid), 비타민B1질산염, 산화마그네슘, 비타민C, 치자청색소, DL-사과산, 야채향, 구연산, 과.채가공품, 비타민 A 혼합제제, 판토텐산칼슘, 건조효모, 니코틴산아미드, 건조효모, 비타민K2, 나한과추출물분말, 파인애플추출분말, 콜레우스포스콜리뿌리, 비타민D3혼합제제, 후추추출물분말, 비타민B6염산염, 유산균혼합분말, 비타민B2, 엽산, 프락토올리고당, 덱스트린, 에리스리톨, 혼합버섯균사체추출물분말, 곡류혼합효소분말, 효소처리스테비아, 효모, 비타민B12, 혼합제제, 비오틴 혼합, 글루콘산아연, 건조효모, 효모추출분말, 케르세틴</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20020496004190</t>
+          <t>19930294014571</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2596,44 +4922,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20020496004</t>
+          <t>19930294014</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>발효흑천마 녹용홍삼골드</t>
+          <t>프리미엄 가나 치즈&amp;티라미수</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>무주덕유산반딧골영농조합법인</t>
+          <t>(주)대웅</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>천마추출액, 칡농축액, 익모초농축액, 식물혼합농축액, L-알라닌, 천궁농축액, 참당귀농축액, 타우린, 액상과당, 녹용추출액, 발효홍삼농축액, 산화마그네슘, 비타민B6염산염, 비타민B1질산염</t>
+          <t>식물성크림, 기타코코아가공품, 과자, 코코아분말</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>200303950191030</t>
+          <t>19960188088985</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2643,44 +4969,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20030395019</t>
+          <t>19960188088</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>멜라토칸포르테</t>
+          <t>감바스짜파게티 후레이크</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(주)유유헬스케어</t>
+          <t>농심태경(주)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>비타민D3혼합제제, 글리세린지방산에스테르, 레몬밤추출물, 스테아린산마그네슘, 이산화규소, 캐모마일추출물분말, 과.채가공품, 산화마그네슘, 현미배아추출물분말, L-트립토판, L-테아닌(고시형), 치커리뿌리추출물분말, 히드록시프로필메틸셀룰로스, 결정셀룰로스, 체리농축분말, 기타가공품</t>
+          <t>과.채가공품, 기타가공품, 어묵</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>200303950191031</t>
+          <t>199804430142154</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2690,32 +5016,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20030395019</t>
+          <t>19980443014</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>케르세틴혼합분말</t>
+          <t>카라멜라이즈드어니언</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(주)유유헬스케어</t>
+          <t>씨제이제일제당(주)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>케르세틴, 덱스트린</t>
+          <t>양파, 갈색설탕, 정제수, 젖산칼슘, 콩기름(대두유), 마늘가루, 볶음양파분말, 당류가공품, 잔탄검</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2727,7 +5053,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20070309132986</t>
+          <t>19990211056279</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2737,32 +5063,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20070309132</t>
+          <t>19990211056</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>꾸찌뽕 발효식초 분말</t>
+          <t>핑크퐁 아이비타C+아연</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(주)코리아화인에프티</t>
+          <t>다이식품 제2공장</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>비타민C, 과.채가공품</t>
+          <t>효소처리스테비아, 산화아연, 구연산, DL-사과산, 스테아린산마그네슘, 과.채가공품, 자일리톨, 비타민C, 포도당</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2774,7 +5100,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20100211096169</t>
+          <t>20020496004190</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2784,44 +5110,44 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20100211096</t>
+          <t>20020496004</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>루틴 식이섬유 그린구미</t>
+          <t>발효흑천마 녹용홍삼골드</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>다이식품</t>
+          <t>무주덕유산반딧골영농조합법인</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>혼합제제, 과.채가공품, 올리고당, 효소처리스테비아, 향료, 과.채가공품, 구연산, D-소비톨액, 에리스리톨, 젤라틴, 정제수, 당류가공품, 난소화성말토덱스트린(고시형), 펙틴, 구연산삼나트륨, 기타 식용유지가공품, 글리세린지방산에스테르, 혼합제제</t>
+          <t>천마추출액, 칡농축액, 익모초농축액, 식물혼합농축액, L-알라닌, 천궁농축액, 참당귀농축액, 타우린, 액상과당, 녹용추출액, 발효홍삼농축액, 산화마그네슘, 비타민B6염산염, 비타민B1질산염</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20230609874618</t>
+          <t>200201832821572</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2831,44 +5157,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20230609874</t>
+          <t>20020183282</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MBP 유단백</t>
+          <t>TS솔티드카라멜시럽(1.2KG)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(주)뉴트리션바이오</t>
+          <t>(주)푸드웰</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>유함유가공품, 프락토올리고당, 유함유가공품, 포도당, 락토페린농축물, 기타가공품, 혼합제제, 산화마그네슘, 유함유가공품, L-프롤린, 유함유가공품, 콜라겐분말, 밀크향분말, 유청단백분말, 분리대두단백</t>
+          <t>기타가공품, 향료, 정제소금, 설탕, 정제수, 향료, 당류가공품, 혼합제제, 구연산, 메타인산나트륨, 소브산칼륨</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025046602637</t>
+          <t>200303950191032</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2878,84 +5204,2763 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20250466026</t>
+          <t>20030395019</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>혼합차</t>
+          <t>락토바실러스플란타룸LB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(주)비오팜2공장</t>
+          <t>(주)유유헬스케어</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>기타 농산가공품, 기타가공품, 기타가공품, 기타가공품, 정제수, 고형차, 스테비올배당체, 기타가공품, 기타가공품</t>
+          <t>덱스트린, 유산균</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>200303950191030</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20030395019</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>멜라토칸포르테</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>(주)유유헬스케어</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>비타민D3혼합제제, 글리세린지방산에스테르, 레몬밤추출물, 스테아린산마그네슘, 이산화규소, 캐모마일추출물분말, 과.채가공품, 산화마그네슘, 현미배아추출물분말, L-트립토판, L-테아닌(고시형), 치커리뿌리추출물분말, 히드록시프로필메틸셀룰로스, 결정셀룰로스, 체리농축분말, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>수면</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>200303950191031</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20030395019</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>케르세틴혼합분말</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>(주)유유헬스케어</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>케르세틴, 덱스트린</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20030467180168</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20030467180</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AS 코어쉘 펩타이드</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>(주)대화바이오</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>기타가공품, 패각분말, 정제수</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20030364667168</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20030364667</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>스파클링 톡톡 깔라만시</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>(주)에이치엘사이언스</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>구연산(무수), 난소화성말토덱스트린(고시형), 탄산수소나트륨, 과.채가공품류, 비타민C, 혼합제제, 포도당, 메이플시럽분말, 아스파탐, 유청칼슘, 치자황색소, 혼합제제, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20050614233730</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20050614233</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>UMK 프리믹스</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>씨제이제일제당(주)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>정제소금, 백설탕, 혼합제제, 밀가루, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20060415215398</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20060415215</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>플라세넥스 발효 양태반복합물M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>주식회사 노바렉스 2공장</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>마카추출분말, 침향나무수지가침착된수간목, 녹용발효추출분말, 유자향, 레몬에이드향, 구연산(무수), DL-사과산, 산화아연, 스테비올배당체, 비타민B6염산염, 비타민B1염산염, 비타민B2, 기타가공품, 연어이리추출물, 불로초자실체, 아미노산혼합분말, 비타민C, 생선콜라겐펩타이드, 식용누에고치단백가수분해물, 브로콜리추출물분말, 과일채소혼합농축액, 기타가공품, L-로이신, L-아르지닌, 정제수</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20070309132986</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20070309132</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>꾸찌뽕 발효식초 분말</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(주)코리아화인에프티</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>비타민C, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20090395056146</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20090395056</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>더덕쉐이크분말</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>횡성인삼영농조합법인</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>정제소금, 더덕뿌리분말, 이눌린/치커리추출물(고시형), 식물성크림, 프락토올리고당</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20090624059789</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>20090624059</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>칸씨슬 파워</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)힐링팜</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>헛개나무열매추출분말, 정제수, 배농축액, 프락토올리고당, 사양벌꿀, 혼합제제, 향료, 효소처리스테비아, 기타가공품, 혼합제제, 강황추출물분말, 구연산(결정), 식물혼합농축액, L-아르지닌, 과.채가공품, 니코틴산아미드, 판토텐산칼슘, 비타민B1염산염, 비타민B2, 비타민B6염산염, 혼합제제, 효모추출물</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20090458111429</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20090458111</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>레드와인비니거분말</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>(주)화인에프티</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>발효식초, 덱스트린</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20100211096169</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20100211096</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>루틴 식이섬유 그린구미</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>다이식품</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>혼합제제, 과.채가공품, 올리고당, 효소처리스테비아, 향료, 과.채가공품, 구연산, D-소비톨액, 에리스리톨, 젤라틴, 정제수, 당류가공품, 난소화성말토덱스트린(고시형), 펙틴, 구연산삼나트륨, 기타 식용유지가공품, 글리세린지방산에스테르, 혼합제제</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20100395093231</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20100395093</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>딸기조아</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>영농조합법인 산골농장</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>딸기</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20100443196523</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20100443196</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>아로니아분말</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>베이시스푸드(주)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>아로니아열매</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20120435086249</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>20120435086</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>올데이 블랙마카</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>(주)원일바이오</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>비타민B1염산염, 산화아연, 판토텐산칼슘, 니코틴산아미드, 스테아린산마그네슘, 이산화규소, 생강추출분말, 흑마늘분말, 타우린, 비수리추출분말, 유채씨앗, 마카뿌리분말, 분말비타민D3혼합제제, 비타민 B12 혼합제제분말, 후추추출물, 비타민B6염산염, 비타민B2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>남성건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20120435086250</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20120435086</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>올데이 페누그릭</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>(주)원일바이오</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>흑마늘분말, 복분자추출물분말, 비수리추출분말, 유채씨앗, 호로파씨추출분말, 분말비타민D3혼합제제, 비타민 B12 혼합제제분말, 후추추출물, 판토텐산칼슘, 비타민B6염산염, 비타민B2, 비타민B1염산염, 산화아연, 니코틴산아미드, 스테아린산마그네슘, 이산화규소, 홍삼농축액분말</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>남성건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2012046412397</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>20120464123</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>향지촌 딸기발효청초</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>향지촌</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>발효식초, 딸기발효액</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20130275074609</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20130275074</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>티요 초코 프로틴 파우더</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>(주)에프비신영</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>향료, 기타가공품, 향료, 코코아분말, 혼합분유, 코코아분말, 식물성크림, 코코아분말, 유청단백분말, 설탕, 잔탄검, 제삼인산칼슘, 정제소금</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>201504420251389</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20150442025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>엔-졸빗파우더블렌드</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>주식회사 하람</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>결정셀룰로스, 당류가공품</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2017028888026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20170288880</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>베이커너</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>마더랩컴퍼니</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>스테비올배당체, 효소처리스테비아, 에리스리톨, 알룰로오스</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2017028888025</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20170288880</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>아루비아</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>마더랩컴퍼니</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>나한과추출물분말, 스테비올배당체, 효소처리스테비아, 알룰로오스, 에리스리톨</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20180442157212</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20180442157</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>덴티조이 프레쉬 구강유산균</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>(주)메디오젠충주공장</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>혼합제제, 결정셀룰로스, 혼합제제, D-소비톨, 이소말트, 프로바이오틱스(고시형), 비타민B2, 건조효모(비타민D), 구연산, 향료, 산화아연, 스테아린산마그네슘, 비타민C, Lacticaseibacillus rhamnosus(고시형)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>구강</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2019055809097</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20190558090</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>온보당 쌍화</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>농업회사법인주식회사부성</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>정제수, 작약뿌리, 대추, 참당귀뿌리, 천궁뿌리줄기, 계피, 지황포제가공한뿌리, 생강, 황기, 감초, 칡뿌리</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2019044604969</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20190446049</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>나물인 국내산 우엉채</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>(주)정화</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 우엉채</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2019044604972</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20190446049</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>나물인국내산배추우거지</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>(주)정화</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 배추잎</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2019044604970</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20190446049</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>나물인 국내산연근채</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>(주)정화</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 연근</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2019041805425</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20190418054</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>홍매실 발사믹</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>발효식초</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>농업회사법인 (주)해밀바이오</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>당절임, 발효식초</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2019041805424</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20190418054</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>아로니아 발사믹</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>발효식초</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>농업회사법인 (주)해밀바이오</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>발효식초, 아로니아농축액</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20190498210527</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20190498210</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>셀비움</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>(주)한풍네이처팜</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20190424102371</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20190424102</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>데이타민 리포좀 글루타씨온</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>광동헬스바이오(주) 2공장</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>밀크씨슬분말, 글리신, L-글루타민, 효모식품, 수크랄로스, 혼합제제, 레몬과즙분말, 자일리톨, 효소처리스테비아, 탄산칼슘, 대나무수액, 레몬향, 레몬라임향, 비타민B2, 에리스리톨, 비타민C</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20200424065169</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20200424065</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>쥬비스 데일리 PDRN 온 미</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>광동헬스바이오(주)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>히알루론산, 엘라스틴가수분해물, 과.채가공품, 기타가공품, 비타민A혼합분말, 생선콜라겐, 효모식품, 비타민C혼합분말, 황금추출물, 구연산, 사과향, 효소처리스테비아, 사과향, 젖산칼슘, 연어이리추출물, DL-사과산, 구연산삼나트륨, 당류가공품, 검베이스, 사과식이섬유, 자일리톨, 용설란시럽, 레몬주스, 사과농축액, 사과농축액, 프락토올리고당, 정제수</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>202004981403</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20200498140</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>생강 콜라겐펩타이드 (농축액)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>(주)쓰리에프씨(3FC)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>정제수, 생강, 넙치껍질</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20210606928254</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20210606928</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>노엘 퓨어 배도라지즙</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>주식회사 마루바이오</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>도라지뿌리추출액, 배농축액, 사양벌꿀</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>면역</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2021047917542</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20210479175</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>건강을 담은 태안 와송 진액</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>태안농산물가공영농조합법인</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>바위솔지상부, 정제수</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20220520003115</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20220520003</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>생녹용골드</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>유에스바이오텍</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>식물혼합추출물</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20220777039212</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>20220777039</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>샐러리컷팅</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>행복한200프로주식회사</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>셀러리</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>202206834731948</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>매스틱 혼합 분말</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>이눌린(고시형), 포도당, 덱스트린, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 과.채가공품, 과.채가공품, 기타가공품, 혼합제제, 기타 농산가공품, 효소식품, 기타가공품, 식품첨가물혼합제제</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>202206834731942</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>업매스틱 복합물</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>식품첨가물, 식품첨가물, 식품첨가물, 효소식품, 기타가공품, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 이눌린(고시형), 덱스트린, 식품첨가물, 식품첨가물, 혼합제제, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2022019969530</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>20220199695</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>바질식초</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>발효식초</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>청향</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>기타설탕, 발효식초, 레몬, 바질줄기</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20230528144361</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>20230528144</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>듀얼 마그네슘</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>바이오디피씨(주)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>DL-사과산, 효소처리스테비아, L-젖산마그네슘, 구연산(무수), 이산화규소, 파인애플맛분말, 파인애플향분말, 파인애플농축, 글루콘산마그네슘, 자일리톨, 포도당</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20230528144364</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>20230528144</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>복합종자유지오일분말</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>바이오디피씨(주)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>중쇄중성지방유, 호박씨앗추출분말, 포도종자추출물</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20230528144363</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>20230528144</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>루버스복분자혼합분말</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>바이오디피씨(주)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>라즈베리농축분말, 복분자추출물분말</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20230612332356</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>20230612332</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>골드 발효 효소 with 카무트®브랜드밀</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>효소식품</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>(주)웰레스트</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>효소식품, 포도당, 곡류가공품, 덱스트린, 볶은콩가루, 분리대두단백, 효소식품, 비타민미네랄혼합제제, 과.채가공품, 제삼인산칼슘, 이산화규소, 고구마향분말, 덱스트린</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>효소</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20230609874618</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>20230609874</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MBP 유단백</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>(주)뉴트리션바이오</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>유함유가공품, 프락토올리고당, 유함유가공품, 포도당, 락토페린농축물, 기타가공품, 혼합제제, 산화마그네슘, 유함유가공품, L-프롤린, 유함유가공품, 콜라겐분말, 밀크향분말, 유청단백분말, 분리대두단백</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025046602637</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>20250466026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>혼합차</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>(주)비오팜2공장</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>기타 농산가공품, 기타가공품, 기타가공품, 기타가공품, 정제수, 고형차, 스테비올배당체, 기타가공품, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>202507181332</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>20250718133</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>청양멜론발사믹</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>발효식초</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>나눔영농조합법인</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>20261001</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>잔탄검, 프락토올리고당, 발효식초, 발효식초, 효모, 설탕, 멜론</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20250470999196</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>20250470999</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>리포좀 피스타치오 복합분말</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>주식회사 비에스바이오</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>서양고추나물잎, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026085525712</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>20260855257</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>연화의 아침곡물</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>연화단지</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>볶은현미, 볶은흑미, 볶은찰보리, 볶음현미찹쌀, 볶은검정콩, 볶음백태, 볶은수수, 볶은율무</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>202603780408</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>20260378040</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>척스 바닐라 빈 시럽</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>쓰리몽키팩토리</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>천일염, 바닐라빈, 당류가공품, 당류가공품, 백설탕, 갈색설탕, 정제수</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>19930294014572</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>19930294014</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>슬리플러스 캄 앤 릴랙스 구미 (SleePlus Calm&amp;Relax Gummies)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>(주)대웅</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>펙틴, 당류가공품, 말티톨시럽, 블루베리농축액, 고형차, 분말셀룰로스, 과.채가공품, 카라기난, 기타 식용유지가공품, 구연산삼나트륨, 향료, 기타가공품, 구연산, 테아닌, 정제수, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>19940484239324</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>19940484239</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>탱글탱글 청사과맛</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>서주푸드 주식회사</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>기타 식용유지가공품, 젖산칼슘, 산도조절제, 향료, 향료, 산도조절제, 산도조절제, 기타가공품, 젤란검, 글리세린, 설탕, 물엿, 정제수, 과.채가공품, 혼합제제, 잔탄검, 로커스트콩검, 펙틴, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>200303950191033</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>20030395019</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>호로파종자추출물</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>(주)유유헬스케어</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>호로파종자추출물(TestofenⓇ)(기능성원료인정제2019-15호), 덱스트린</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>남성건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>200303950191034</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>20030395019</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>수용성 리포좀 커큐민 강황 프로맥스</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>(주)유유헬스케어</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>포도당, 기타 농산가공품, 결정셀룰로스, 생선콜라겐, 기타가공품, L-아르지닌, 비타민C, 밀크씨슬추출물분말, 글리세린지방산에스테르, 치커리뿌리추출물분말, 후추추출물분말, 제삼인산칼슘, 카나우바왁스, 히드록시프로필메틸셀룰로스, 기타 농산가공품, 기타가공품, 해조칼슘</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20140344199681</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>20140344199</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>자바칩 X2 파우더</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>주식회사 디스다임</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>향료, 아미드펙틴, 카복시메틸셀룰로스나트륨, 구아검, 잔탄검, 카라기난, 효소처리스테비아, 향료, 정제소금, 덱스트린, 혼합분유, 유청, 인스턴트커피, 코코아분말, 가공유크림, 식물성크림, 식물성크림, 코코아분말, 준초콜릿, 설탕, 레시틴, 이산화규소</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20170528127123</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>20170528127</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>참든케어 유기농 수세미 쿨</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>(주)참든건강과학 농업회사법인</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>수세미오이발효액, 매실발효액</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20180037041114</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>20180037041</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>유기농 동결건조 하스카프 베리분말</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>(주)팜투팜2공장</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>댕댕이나무열매</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20180037041128</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>20180037041</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>리바이탈 포스트프로바이오틱스</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>(주)팜투팜2공장</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>치커리뿌리추출물분말, 분말결정포도당, 식물성크림혼합분말, 기타가공품, 프락토올리고당, 아스코르빈산(고시형), 기타가공품, Lactobacillus gasseri, L-프롤린, 유산균혼합분말, 식물혼합발효분말, 비타민미네랄혼합분말</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>장건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20220520255204</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>20220520255</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>우슬, 보스웰리아 환</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>아인팜</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>두충수피, 쇠무릅분말, 보스웰리아추출물, 왕느릅나무껍질, 오갈피나무, 황칠나무, 여주, 뚱딴지, 배초향지상부, 기타가공품, 산수유열매, 전칠삼뿌리, 까마귀쪽나무열매, 삽주뿌리줄기박, 바나바잎</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>관절</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20240672181126</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>20240672181</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>가바 멜라토닌 5mg 함유</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>(주)씨이에스팜</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>로즈마리분말, 레몬밤추출물, 서양고추나물분말, 치커리뿌리추출물, 과.채가공품, 포도당, 해조칼슘, 캐모마일추출물분말, 이산화규소, 비타민C, 카복시메틸셀룰로스칼슘, 스테아린산마그네슘, 산화마그네슘, 테아닌, L-트립토판, 유산균배양건조물, 히알루론산혼합제제</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>수면</t>
         </is>
       </c>
     </row>
@@ -4484,31 +9489,31 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="10" t="n">
+      <c r="J20" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>0</v>
@@ -4526,34 +9531,34 @@
         <v>0</v>
       </c>
       <c r="P20" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R20" s="7" t="n">
-        <v>0</v>
+      <c r="R20" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T20" s="7" t="n">
-        <v>0</v>
+      <c r="T20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U20" s="10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W20" s="10" t="n">
         <v>1</v>
       </c>
       <c r="X20" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
@@ -4563,31 +9568,31 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>-37</v>
+        <v>-35</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>-20</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>-95</v>
+        <v>-87</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>-22</v>
+        <v>-17</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>-38</v>
+        <v>-36</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>-11</v>
@@ -4605,34 +9610,34 @@
         <v>-1</v>
       </c>
       <c r="P21" s="12" t="n">
-        <v>-25</v>
+        <v>-23</v>
       </c>
       <c r="Q21" s="12" t="n">
         <v>-2</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>-2</v>
       </c>
       <c r="T21" s="12" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="U21" s="12" t="n">
-        <v>-72</v>
+        <v>-66</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="W21" s="12" t="n">
         <v>-18</v>
       </c>
-      <c r="X21" s="12" t="n">
-        <v>-1</v>
+      <c r="X21" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>-480</v>
+        <v>-443</v>
       </c>
     </row>
     <row r="22">
@@ -4721,31 +9726,31 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I23" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="C23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>-6</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>-2</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>0</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>0</v>
@@ -4763,34 +9768,34 @@
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="Q23" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="10" t="n">
-        <v>0</v>
+      <c r="R23" s="12" t="n">
+        <v>-3</v>
       </c>
       <c r="S23" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="10" t="n">
-        <v>0</v>
+      <c r="T23" s="12" t="n">
+        <v>-1</v>
       </c>
       <c r="U23" s="12" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W23" s="12" t="n">
         <v>-1</v>
       </c>
       <c r="X23" s="12" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>-30</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="24">
@@ -6150,62 +11155,62 @@
           <t>10월</t>
         </is>
       </c>
-      <c r="B47" s="7" t="n">
-        <v>0</v>
+      <c r="B47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="C47" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="F47" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I47" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="7" t="n">
-        <v>0</v>
+      <c r="J47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="K47" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="L47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="O47" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P47" s="7" t="n">
-        <v>0</v>
+      <c r="P47" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="Q47" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R47" s="7" t="n">
-        <v>0</v>
+      <c r="R47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="S47" s="10" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="T47" s="8" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
@@ -6215,61 +11220,61 @@
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>-35</v>
+        <v>-33</v>
       </c>
       <c r="C48" s="12" t="n">
-        <v>-55</v>
+        <v>-53</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>-71</v>
+        <v>-70</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>-34</v>
+        <v>-33</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>-112</v>
+        <v>-107</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>-1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="I48" s="12" t="n">
         <v>-37</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>-37</v>
+        <v>-36</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>-12</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>-53</v>
+        <v>-50</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="O48" s="12" t="n">
         <v>-6</v>
       </c>
       <c r="P48" s="12" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="Q48" s="12" t="n">
         <v>-12</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>-63</v>
+        <v>-62</v>
       </c>
       <c r="S48" s="12" t="n">
-        <v>-1005</v>
+        <v>-970</v>
       </c>
       <c r="T48" s="12" t="n">
-        <v>-1606</v>
+        <v>-1549</v>
       </c>
     </row>
     <row r="49">
@@ -6342,62 +11347,62 @@
           <t>전월대비</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n">
-        <v>0</v>
+      <c r="B50" s="12" t="n">
+        <v>-2</v>
       </c>
       <c r="C50" s="12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E50" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="F50" s="12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="E50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="I50" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="10" t="n">
-        <v>0</v>
+      <c r="J50" s="12" t="n">
+        <v>-1</v>
       </c>
       <c r="K50" s="12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N50" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="L50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O50" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="P50" s="10" t="n">
-        <v>0</v>
+      <c r="P50" s="12" t="n">
+        <v>-3</v>
       </c>
       <c r="Q50" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="R50" s="10" t="n">
-        <v>0</v>
+      <c r="R50" s="12" t="n">
+        <v>-1</v>
       </c>
       <c r="S50" s="12" t="n">
-        <v>-7</v>
+        <v>-42</v>
       </c>
       <c r="T50" s="12" t="n">
-        <v>-10</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="51">

--- a/output/2026-10_품목신고보고현황.xlsx
+++ b/output/2026-10_품목신고보고현황.xlsx
@@ -4754,7 +4754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4762,7 +4762,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
@@ -6228,7 +6228,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2019055809097</t>
+          <t>20190456003388</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6238,32 +6238,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20190558090</t>
+          <t>20190456003</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>온보당 쌍화</t>
+          <t>유기농 화이트와인비니거</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>농업회사법인주식회사부성</t>
+          <t>농업회사법인주식회사에프앤비바이오</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>정제수, 작약뿌리, 대추, 참당귀뿌리, 천궁뿌리줄기, 계피, 지황포제가공한뿌리, 생강, 황기, 감초, 칡뿌리</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2019044604969</t>
+          <t>2019055809097</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6285,22 +6285,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20190446049</t>
+          <t>20190558090</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>나물인 국내산 우엉채</t>
+          <t>온보당 쌍화</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>(주)정화</t>
+          <t>농업회사법인주식회사부성</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>젖산칼슘, 비타민C, 구연산, 정제수, 우엉채</t>
+          <t>정제수, 작약뿌리, 대추, 참당귀뿌리, 천궁뿌리줄기, 계피, 지황포제가공한뿌리, 생강, 황기, 감초, 칡뿌리</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -6322,7 +6322,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2019044604972</t>
+          <t>2019044604969</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>나물인국내산배추우거지</t>
+          <t>나물인 국내산 우엉채</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>젖산칼슘, 비타민C, 구연산, 정제수, 배추잎</t>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 우엉채</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -6369,7 +6369,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2019044604970</t>
+          <t>2019044604972</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>나물인 국내산연근채</t>
+          <t>나물인국내산배추우거지</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>젖산칼슘, 비타민C, 구연산, 정제수, 연근</t>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 배추잎</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2019041805425</t>
+          <t>2019044604970</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20190418054</t>
+          <t>20190446049</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>홍매실 발사믹</t>
+          <t>나물인 국내산연근채</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>농업회사법인 (주)해밀바이오</t>
+          <t>(주)정화</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>당절임, 발효식초</t>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 연근</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2019041805424</t>
+          <t>2019041805425</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>아로니아 발사믹</t>
+          <t>홍매실 발사믹</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6498,19 +6498,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>발효식초, 아로니아농축액</t>
+          <t>당절임, 발효식초</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20190498210527</t>
+          <t>2019041805424</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6520,22 +6520,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20190498210</t>
+          <t>20190418054</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>셀비움</t>
+          <t>아로니아 발사믹</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>(주)한풍네이처팜</t>
+          <t>농업회사법인 (주)해밀바이오</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -6545,19 +6545,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>발효식초, 아로니아농축액</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20190424102371</t>
+          <t>20190498210527</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20190424102</t>
+          <t>20190498210</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>데이타민 리포좀 글루타씨온</t>
+          <t>셀비움</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>광동헬스바이오(주) 2공장</t>
+          <t>(주)한풍네이처팜</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>밀크씨슬분말, 글리신, L-글루타민, 효모식품, 수크랄로스, 혼합제제, 레몬과즙분말, 자일리톨, 효소처리스테비아, 탄산칼슘, 대나무수액, 레몬향, 레몬라임향, 비타민B2, 에리스리톨, 비타민C</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20200424065169</t>
+          <t>20190424102371</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6614,22 +6614,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20200424065</t>
+          <t>20190424102</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>쥬비스 데일리 PDRN 온 미</t>
+          <t>데이타민 리포좀 글루타씨온</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>광동헬스바이오(주)</t>
+          <t>광동헬스바이오(주) 2공장</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -6639,19 +6639,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>히알루론산, 엘라스틴가수분해물, 과.채가공품, 기타가공품, 비타민A혼합분말, 생선콜라겐, 효모식품, 비타민C혼합분말, 황금추출물, 구연산, 사과향, 효소처리스테비아, 사과향, 젖산칼슘, 연어이리추출물, DL-사과산, 구연산삼나트륨, 당류가공품, 검베이스, 사과식이섬유, 자일리톨, 용설란시럽, 레몬주스, 사과농축액, 사과농축액, 프락토올리고당, 정제수</t>
+          <t>밀크씨슬분말, 글리신, L-글루타민, 효모식품, 수크랄로스, 혼합제제, 레몬과즙분말, 자일리톨, 효소처리스테비아, 탄산칼슘, 대나무수액, 레몬향, 레몬라임향, 비타민B2, 에리스리톨, 비타민C</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>202004981403</t>
+          <t>20200424065169</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6661,22 +6661,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>20200498140</t>
+          <t>20200424065</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>생강 콜라겐펩타이드 (농축액)</t>
+          <t>쥬비스 데일리 PDRN 온 미</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>(주)쓰리에프씨(3FC)</t>
+          <t>광동헬스바이오(주)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>정제수, 생강, 넙치껍질</t>
+          <t>히알루론산, 엘라스틴가수분해물, 과.채가공품, 기타가공품, 비타민A혼합분말, 생선콜라겐, 효모식품, 비타민C혼합분말, 황금추출물, 구연산, 사과향, 효소처리스테비아, 사과향, 젖산칼슘, 연어이리추출물, DL-사과산, 구연산삼나트륨, 당류가공품, 검베이스, 사과식이섬유, 자일리톨, 용설란시럽, 레몬주스, 사과농축액, 사과농축액, 프락토올리고당, 정제수</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6698,7 +6698,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20210606928254</t>
+          <t>202004981403</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6708,22 +6708,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>20210606928</t>
+          <t>20200498140</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>노엘 퓨어 배도라지즙</t>
+          <t>생강 콜라겐펩타이드 (농축액)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>주식회사 마루바이오</t>
+          <t>(주)쓰리에프씨(3FC)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6733,19 +6733,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>도라지뿌리추출액, 배농축액, 사양벌꿀</t>
+          <t>정제수, 생강, 넙치껍질</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2021047917542</t>
+          <t>20210606928254</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>20210479175</t>
+          <t>20210606928</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>건강을 담은 태안 와송 진액</t>
+          <t>노엘 퓨어 배도라지즙</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>태안농산물가공영농조합법인</t>
+          <t>주식회사 마루바이오</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6780,19 +6780,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>바위솔지상부, 정제수</t>
+          <t>도라지뿌리추출액, 배농축액, 사양벌꿀</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20220520003115</t>
+          <t>2021047917542</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20220520003</t>
+          <t>20210479175</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>생녹용골드</t>
+          <t>건강을 담은 태안 와송 진액</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>유에스바이오텍</t>
+          <t>태안농산물가공영농조합법인</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6827,19 +6827,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>식물혼합추출물</t>
+          <t>바위솔지상부, 정제수</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20220777039212</t>
+          <t>20220520003115</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6849,22 +6849,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>20220777039</t>
+          <t>20220520003</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>샐러리컷팅</t>
+          <t>생녹용골드</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>행복한200프로주식회사</t>
+          <t>유에스바이오텍</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6874,19 +6874,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>셀러리</t>
+          <t>식물혼합추출물</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>202206834731948</t>
+          <t>20220777039212</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6896,22 +6896,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>20220683473</t>
+          <t>20220777039</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>매스틱 혼합 분말</t>
+          <t>샐러리컷팅</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>주식회사 에이브바이오랩스</t>
+          <t>행복한200프로주식회사</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>이눌린(고시형), 포도당, 덱스트린, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 과.채가공품, 과.채가공품, 기타가공품, 혼합제제, 기타 농산가공품, 효소식품, 기타가공품, 식품첨가물혼합제제</t>
+          <t>셀러리</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6933,7 +6933,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>202206834731942</t>
+          <t>202206834731957</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>업매스틱 복합물</t>
+          <t>파라다이스 그레인 프리미엄 포뮬라</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>식품첨가물, 식품첨가물, 식품첨가물, 효소식품, 기타가공품, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 이눌린(고시형), 덱스트린, 식품첨가물, 식품첨가물, 혼합제제, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품, 기타가공품</t>
+          <t>식품첨가물, 식품첨가물, 과.채가공품, 두류가공품, 기타가공품, 효소식품, 기타가공품, 기타 농산가공품, 이눌린(고시형), 식품첨가물, 덱스트린, 난소화성말토덱스트린(고시형), 올리고당, 과.채가공품</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6980,7 +6980,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2022019969530</t>
+          <t>202206834731967</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6990,32 +6990,32 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>20220199695</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>바질식초</t>
+          <t>핏브라운맥스</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>청향</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>기타설탕, 발효식초, 레몬, 바질줄기</t>
+          <t>기타 농산가공품, 식품첨가물, 덱스트린, 이눌린(고시형), 식품첨가물, 식품첨가물, 기타가공품, 기타가공품, 기타가공품, 기타가공품, 기타가공품, 기타가공품, 식품첨가물, 과.채가공품, 식품첨가물</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7027,7 +7027,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20230528144361</t>
+          <t>202206834731948</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7037,22 +7037,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>듀얼 마그네슘</t>
+          <t>매스틱 혼합 분말</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>DL-사과산, 효소처리스테비아, L-젖산마그네슘, 구연산(무수), 이산화규소, 파인애플맛분말, 파인애플향분말, 파인애플농축, 글루콘산마그네슘, 자일리톨, 포도당</t>
+          <t>이눌린(고시형), 포도당, 덱스트린, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 과.채가공품, 과.채가공품, 기타가공품, 혼합제제, 기타 농산가공품, 효소식품, 기타가공품, 식품첨가물혼합제제</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7074,7 +7074,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20230528144364</t>
+          <t>202206834731971</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7084,44 +7084,44 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>복합종자유지오일분말</t>
+          <t>폴리코사놀s 포뮬라</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>중쇄중성지방유, 호박씨앗추출분말, 포도종자추출물</t>
+          <t>식품첨가물, 식품첨가물, 기타가공품, 덱스트린, 이눌린/치커리추출물(고시형)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20230528144363</t>
+          <t>202206834731955</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7131,44 +7131,44 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>루버스복분자혼합분말</t>
+          <t>그린아세로라c 추출분말 복합물</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>라즈베리농축분말, 복분자추출물분말</t>
+          <t>과.채가공품, 과.채가공품, 식품첨가물, 식품첨가물, 포도당, 덱스트린, 이눌린/치커리추출물(고시형), 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 식품첨가물</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20230612332356</t>
+          <t>202206834731969</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7178,44 +7178,44 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>20230612332</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>골드 발효 효소 with 카무트®브랜드밀</t>
+          <t>매스틱 맥스</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>효소식품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>(주)웰레스트</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>효소식품, 포도당, 곡류가공품, 덱스트린, 볶은콩가루, 분리대두단백, 효소식품, 비타민미네랄혼합제제, 과.채가공품, 제삼인산칼슘, 이산화규소, 고구마향분말, 덱스트린</t>
+          <t>식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 덱스트린, 식품첨가물, 식품첨가물, 혼합제제, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품, 효소식품, 기타가공품, 이눌린(고시형)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>효소</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20230609874618</t>
+          <t>202206834731965</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7225,44 +7225,44 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>20230609874</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MBP 유단백</t>
+          <t>위하는 매스틱 포뮬러</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>(주)뉴트리션바이오</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>유함유가공품, 프락토올리고당, 유함유가공품, 포도당, 락토페린농축물, 기타가공품, 혼합제제, 산화마그네슘, 유함유가공품, L-프롤린, 유함유가공품, 콜라겐분말, 밀크향분말, 유청단백분말, 분리대두단백</t>
+          <t>덱스트린, 맥문동추출물, 기타가공품, 과.채가공품, 식품첨가물, 덱스트린, 포도당, 이눌린(고시형), 과.채가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 기타가공품, 효소식품, 식품첨가물혼합제제, 기타가공품, 혼합제제</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025046602637</t>
+          <t>202206834731959</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7272,32 +7272,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>20250466026</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>혼합차</t>
+          <t>파라다이스 그레인 프리미엄 복합물</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>(주)비오팜2공장</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>기타 농산가공품, 기타가공품, 기타가공품, 기타가공품, 정제수, 고형차, 스테비올배당체, 기타가공품, 기타가공품</t>
+          <t>기타가공품, 두류가공품, 기타가공품, 과.채가공품, 식품첨가물, 기타 농산가공품, 과.채가공품, 식품첨가물, 덱스트린, 이눌린(고시형), 과.채가공품, 유함유가공품, 식품첨가물</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7309,7 +7309,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>202507181332</t>
+          <t>202206834731963</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7319,32 +7319,32 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>20250718133</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>청양멜론발사믹</t>
+          <t>젖산 마그네슘 액티브 포뮬러</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>발효식초</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>나눔영농조합법인</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>잔탄검, 프락토올리고당, 발효식초, 발효식초, 효모, 설탕, 멜론</t>
+          <t>식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 당류가공품, 이눌린/치커리추출물(고시형)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7356,7 +7356,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20250470999196</t>
+          <t>202206834731942</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7366,22 +7366,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>20250470999</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>리포좀 피스타치오 복합분말</t>
+          <t>업매스틱 복합물</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>주식회사 비에스바이오</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>서양고추나물잎, 기타가공품</t>
+          <t>식품첨가물, 식품첨가물, 식품첨가물, 효소식품, 기타가공품, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 이눌린(고시형), 덱스트린, 식품첨가물, 식품첨가물, 혼합제제, 과.채가공품, 기타가공품, 과.채가공품, 기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7403,7 +7403,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026085525712</t>
+          <t>202206834731961</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7413,32 +7413,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>20260855257</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>연화의 아침곡물</t>
+          <t>매스틱복합물 매스틱 파우더</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>연화단지</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>볶은현미, 볶은흑미, 볶은찰보리, 볶음현미찹쌀, 볶은검정콩, 볶음백태, 볶은수수, 볶은율무</t>
+          <t>과.채가공품, 이눌린(고시형), 난소화성말토덱스트린(고시형), 덱스트린, 식품첨가물, 혼합제제, 과.채가공품, 기타가공품, 식품첨가물혼합제제, 기타가공품, 효소식품, 기타가공품, 과.채가공품, 식품첨가물, 과.채가공품</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7450,7 +7450,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>202603780408</t>
+          <t>2022068347741</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7460,69 +7460,69 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>20260378040</t>
+          <t>20220683477</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>척스 바닐라 빈 시럽</t>
+          <t>순수 PDRN 플러스(+)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>쓰리몽키팩토리</t>
+          <t>(주)렉스팜</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>천일염, 바닐라빈, 당류가공품, 당류가공품, 백설탕, 갈색설탕, 정제수</t>
+          <t>이산화규소, 효모추출물, 레몬맛분말, 유당, 생선콜라겐, 포도당, 기타엿, 엘라스틴가수분해물, 히알루론산(고시형), 연어이리추출물, 유산균혼합분말</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19930294014572</t>
+          <t>2022019969530</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>19930294014</t>
+          <t>20220199695</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>슬리플러스 캄 앤 릴랙스 구미 (SleePlus Calm&amp;Relax Gummies)</t>
+          <t>바질식초</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>발효식초</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>(주)대웅</t>
+          <t>청향</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -7532,44 +7532,44 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>펙틴, 당류가공품, 말티톨시럽, 블루베리농축액, 고형차, 분말셀룰로스, 과.채가공품, 카라기난, 기타 식용유지가공품, 구연산삼나트륨, 향료, 기타가공품, 구연산, 테아닌, 정제수, 기타가공품</t>
+          <t>기타설탕, 발효식초, 레몬, 바질줄기</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19940484239324</t>
+          <t>20230528144361</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>19940484239</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>탱글탱글 청사과맛</t>
+          <t>듀얼 마그네슘</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>서주푸드 주식회사</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>기타 식용유지가공품, 젖산칼슘, 산도조절제, 향료, 향료, 산도조절제, 산도조절제, 기타가공품, 젤란검, 글리세린, 설탕, 물엿, 정제수, 과.채가공품, 혼합제제, 잔탄검, 로커스트콩검, 펙틴, 과.채가공품</t>
+          <t>DL-사과산, 효소처리스테비아, L-젖산마그네슘, 구연산(무수), 이산화규소, 파인애플맛분말, 파인애플향분말, 파인애플농축, 글루콘산마그네슘, 자일리톨, 포도당</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7591,22 +7591,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>200303950191033</t>
+          <t>20230528144364</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>20030395019</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>호로파종자추출물</t>
+          <t>복합종자유지오일분말</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>(주)유유헬스케어</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -7626,44 +7626,44 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>호로파종자추출물(TestofenⓇ)(기능성원료인정제2019-15호), 덱스트린</t>
+          <t>중쇄중성지방유, 호박씨앗추출분말, 포도종자추출물</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>남성건강</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>200303950191034</t>
+          <t>20230528144363</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>20030395019</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>수용성 리포좀 커큐민 강황 프로맥스</t>
+          <t>루버스복분자혼합분말</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>(주)유유헬스케어</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -7673,44 +7673,44 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>포도당, 기타 농산가공품, 결정셀룰로스, 생선콜라겐, 기타가공품, L-아르지닌, 비타민C, 밀크씨슬추출물분말, 글리세린지방산에스테르, 치커리뿌리추출물분말, 후추추출물분말, 제삼인산칼슘, 카나우바왁스, 히드록시프로필메틸셀룰로스, 기타 농산가공품, 기타가공품, 해조칼슘</t>
+          <t>라즈베리농축분말, 복분자추출물분말</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20140344199681</t>
+          <t>20230612332356</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>20140344199</t>
+          <t>20230612332</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>자바칩 X2 파우더</t>
+          <t>골드 발효 효소 with 카무트®브랜드밀</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>효소식품</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>주식회사 디스다임</t>
+          <t>(주)웰레스트</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7720,245 +7720,1044 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>향료, 아미드펙틴, 카복시메틸셀룰로스나트륨, 구아검, 잔탄검, 카라기난, 효소처리스테비아, 향료, 정제소금, 덱스트린, 혼합분유, 유청, 인스턴트커피, 코코아분말, 가공유크림, 식물성크림, 식물성크림, 코코아분말, 준초콜릿, 설탕, 레시틴, 이산화규소</t>
+          <t>효소식품, 포도당, 곡류가공품, 덱스트린, 볶은콩가루, 분리대두단백, 효소식품, 비타민미네랄혼합제제, 과.채가공품, 제삼인산칼슘, 이산화규소, 고구마향분말, 덱스트린</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>효소</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20170528127123</t>
+          <t>20230609874618</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>20230609874</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MBP 유단백</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>(주)뉴트리션바이오</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>20261002</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>20170528127</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>참든케어 유기농 수세미 쿨</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>액상차</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>(주)참든건강과학 농업회사법인</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
-      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>수세미오이발효액, 매실발효액</t>
+          <t>유함유가공품, 프락토올리고당, 유함유가공품, 포도당, 락토페린농축물, 기타가공품, 혼합제제, 산화마그네슘, 유함유가공품, L-프롤린, 유함유가공품, 콜라겐분말, 밀크향분말, 유청단백분말, 분리대두단백</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20180037041114</t>
+          <t>202407427742</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>20180037041</t>
+          <t>20240742774</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>유기농 동결건조 하스카프 베리분말</t>
+          <t>달라티 수국차</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>(주)팜투팜2공장</t>
+          <t>주식회사 코아바이오 2공장</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261004</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>댕댕이나무열매</t>
+          <t>탄산수소나트륨, 바나바잎 추출물(고시형), 비타민C, 침출차, 정제수</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20180037041128</t>
+          <t>2025046602637</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>20250466026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>혼합차</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>(주)비오팜2공장</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>20261002</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>20180037041</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>리바이탈 포스트프로바이오틱스</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>기타가공품</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>(주)팜투팜2공장</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
-      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>치커리뿌리추출물분말, 분말결정포도당, 식물성크림혼합분말, 기타가공품, 프락토올리고당, 아스코르빈산(고시형), 기타가공품, Lactobacillus gasseri, L-프롤린, 유산균혼합분말, 식물혼합발효분말, 비타민미네랄혼합분말</t>
+          <t>기타 농산가공품, 기타가공품, 기타가공품, 기타가공품, 정제수, 고형차, 스테비올배당체, 기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20220520255204</t>
+          <t>202507181332</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>20250718133</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>청양멜론발사믹</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>발효식초</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>나눔영농조합법인</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
           <t>20261002</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>20220520255</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>우슬, 보스웰리아 환</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>기타가공품</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>아인팜</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
-      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>두충수피, 쇠무릅분말, 보스웰리아추출물, 왕느릅나무껍질, 오갈피나무, 황칠나무, 여주, 뚱딴지, 배초향지상부, 기타가공품, 산수유열매, 전칠삼뿌리, 까마귀쪽나무열매, 삽주뿌리줄기박, 바나바잎</t>
+          <t>잔탄검, 프락토올리고당, 발효식초, 발효식초, 효모, 설탕, 멜론</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>20250470999196</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>20250470999</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>리포좀 피스타치오 복합분말</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>주식회사 비에스바이오</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>서양고추나물잎, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026085525712</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>20260855257</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>연화의 아침곡물</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>연화단지</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>볶은현미, 볶은흑미, 볶은찰보리, 볶음현미찹쌀, 볶은검정콩, 볶음백태, 볶은수수, 볶은율무</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>202603780408</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>20260378040</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>척스 바닐라 빈 시럽</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>쓰리몽키팩토리</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>천일염, 바닐라빈, 당류가공품, 당류가공품, 백설탕, 갈색설탕, 정제수</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>19930294014572</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>19930294014</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>슬리플러스 캄 앤 릴랙스 구미 (SleePlus Calm&amp;Relax Gummies)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>(주)대웅</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>펙틴, 당류가공품, 말티톨시럽, 블루베리농축액, 고형차, 분말셀룰로스, 과.채가공품, 카라기난, 기타 식용유지가공품, 구연산삼나트륨, 향료, 기타가공품, 구연산, 테아닌, 정제수, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>19940484239324</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>19940484239</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>탱글탱글 청사과맛</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>캔디류</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>서주푸드 주식회사</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>기타 식용유지가공품, 젖산칼슘, 산도조절제, 향료, 향료, 산도조절제, 산도조절제, 기타가공품, 젤란검, 글리세린, 설탕, 물엿, 정제수, 과.채가공품, 혼합제제, 잔탄검, 로커스트콩검, 펙틴, 과.채가공품</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>200303950191033</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>20030395019</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>호로파종자추출물</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>(주)유유헬스케어</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>호로파종자추출물(TestofenⓇ)(기능성원료인정제2019-15호), 덱스트린</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>남성건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>200303950191034</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>20030395019</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>수용성 리포좀 커큐민 강황 프로맥스</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>(주)유유헬스케어</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>포도당, 기타 농산가공품, 결정셀룰로스, 생선콜라겐, 기타가공품, L-아르지닌, 비타민C, 밀크씨슬추출물분말, 글리세린지방산에스테르, 치커리뿌리추출물분말, 후추추출물분말, 제삼인산칼슘, 카나우바왁스, 히드록시프로필메틸셀룰로스, 기타 농산가공품, 기타가공품, 해조칼슘</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20140344199681</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>20140344199</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>자바칩 X2 파우더</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>주식회사 디스다임</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>향료, 아미드펙틴, 카복시메틸셀룰로스나트륨, 구아검, 잔탄검, 카라기난, 효소처리스테비아, 향료, 정제소금, 덱스트린, 혼합분유, 유청, 인스턴트커피, 코코아분말, 가공유크림, 식물성크림, 식물성크림, 코코아분말, 준초콜릿, 설탕, 레시틴, 이산화규소</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>201504612251583</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>20150461225</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>감귤농축과즙액H</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>해찬솔푸드</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>감귤농축액</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20170624086114</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>20170624086</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>거창한 동결건조 딸기</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>거창농민가공협동조합</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>딸기</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20170449030805</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>20170449030</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>솔엔자임</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>효소식품</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>주식회사 코스팜</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>효소식품, 두류가공품, 효소식품, 기타가공품, 기타가공품, 과.채가공품, 과.채가공품, 과.채가공품, 기타 농산가공품, 기타가공품</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20170528127123</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>20170528127</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>참든케어 유기농 수세미 쿨</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>액상차</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>(주)참든건강과학 농업회사법인</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>수세미오이발효액, 매실발효액</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20180456001968</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>20180456001</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>제주풋귤농축액</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>과.채가공품</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>(주)가온에프앤비</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>감귤과즙</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20180037041114</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>20180037041</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>유기농 동결건조 하스카프 베리분말</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>(주)팜투팜2공장</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>댕댕이나무열매</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20180037041128</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>20180037041</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>리바이탈 포스트프로바이오틱스</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>(주)팜투팜2공장</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>치커리뿌리추출물분말, 분말결정포도당, 식물성크림혼합분말, 기타가공품, 프락토올리고당, 아스코르빈산(고시형), 기타가공품, Lactobacillus gasseri, L-프롤린, 유산균혼합분말, 식물혼합발효분말, 비타민미네랄혼합분말</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>장건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20180037041124</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>20180037041</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>마이오이노시톨40:1프리미엄</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>(주)팜투팜2공장</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>레몬과즙분말, 옥수수전분, 주석산수소콜린, 효소처리스테비아, 비타민D3혼합제제, 비타민B12, 비타민B6염산염, 비타민B2, DL-사과산, 엽산, 기타가공품, 생선콜라겐, L-프롤린, 비타민E혼합제제, 식물혼합발효분말, 구연산삼나트륨, 대나무수액, 레몬향분말, 이노시톨, 분말결정포도당, 비타민C, 캐롭분말</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>여성건강</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20220520255204</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>20220520255</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>우슬, 보스웰리아 환</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>아인팜</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>두충수피, 쇠무릅분말, 보스웰리아추출물, 왕느릅나무껍질, 오갈피나무, 황칠나무, 여주, 뚱딴지, 배초향지상부, 기타가공품, 산수유열매, 전칠삼뿌리, 까마귀쪽나무열매, 삽주뿌리줄기박, 바나바잎</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>관절</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>20240672181126</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>20261002</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>20240672181</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>가바 멜라토닌 5mg 함유</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>과.채가공품</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>(주)씨이에스팜</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>20261003</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>로즈마리분말, 레몬밤추출물, 서양고추나물분말, 치커리뿌리추출물, 과.채가공품, 포도당, 해조칼슘, 캐모마일추출물분말, 이산화규소, 비타민C, 카복시메틸셀룰로스칼슘, 스테아린산마그네슘, 산화마그네슘, 테아닌, L-트립토판, 유산균배양건조물, 히알루론산혼합제제</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>수면</t>
         </is>
@@ -11156,7 +11955,7 @@
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" s="10" t="n">
         <v>3</v>
@@ -11168,7 +11967,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -11180,7 +11979,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" s="10" t="n">
         <v>2</v>
@@ -11194,8 +11993,8 @@
       <c r="N47" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O47" s="7" t="n">
-        <v>0</v>
+      <c r="O47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="P47" s="10" t="n">
         <v>3</v>
@@ -11204,13 +12003,13 @@
         <v>0</v>
       </c>
       <c r="R47" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S47" s="10" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="T47" s="8" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48">
@@ -11220,7 +12019,7 @@
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>-33</v>
+        <v>-32</v>
       </c>
       <c r="C48" s="12" t="n">
         <v>-53</v>
@@ -11232,7 +12031,7 @@
         <v>-33</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>-107</v>
+        <v>-104</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>-1</v>
@@ -11244,7 +12043,7 @@
         <v>-37</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>-36</v>
+        <v>-35</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>-31</v>
@@ -11259,7 +12058,7 @@
         <v>-9</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>-11</v>
@@ -11268,13 +12067,13 @@
         <v>-12</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>-62</v>
+        <v>-61</v>
       </c>
       <c r="S48" s="12" t="n">
-        <v>-970</v>
+        <v>-960</v>
       </c>
       <c r="T48" s="12" t="n">
-        <v>-1549</v>
+        <v>-1532</v>
       </c>
     </row>
     <row r="49">
@@ -11348,7 +12147,7 @@
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C50" s="12" t="n">
         <v>-3</v>
@@ -11360,7 +12159,7 @@
         <v>-1</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -11372,7 +12171,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>-2</v>
@@ -11386,8 +12185,8 @@
       <c r="N50" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="O50" s="10" t="n">
-        <v>0</v>
+      <c r="O50" s="12" t="n">
+        <v>-1</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>-3</v>
@@ -11396,13 +12195,13 @@
         <v>0</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S50" s="12" t="n">
-        <v>-42</v>
+        <v>-52</v>
       </c>
       <c r="T50" s="12" t="n">
-        <v>-67</v>
+        <v>-84</v>
       </c>
     </row>
     <row r="51">

--- a/output/2026-10_품목신고보고현황.xlsx
+++ b/output/2026-10_품목신고보고현황.xlsx
@@ -8912,7 +8912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I309"/>
+  <dimension ref="A1:I312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -11091,7 +11091,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2019044604976</t>
+          <t>2019044604973</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>나물인국내산도라지</t>
+          <t>나물인국내산 고사리</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -11121,24 +11121,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>도라지뿌리, 정제수, 구연산, 비타민C, 젖산칼슘</t>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 삶은고사리</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2019044604973</t>
+          <t>2019044604974</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>나물인국내산 고사리</t>
+          <t>나물인 국내산고구마줄기</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>젖산칼슘, 비타민C, 구연산, 정제수, 삶은고사리</t>
+          <t>비타민C, 젖산칼륨, 정제수, 고구마줄기, 구연산</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11185,7 +11185,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2019044604974</t>
+          <t>2019044604976</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>나물인 국내산고구마줄기</t>
+          <t>나물인국내산도라지</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -11215,24 +11215,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>비타민C, 젖산칼륨, 정제수, 고구마줄기, 구연산</t>
+          <t>도라지뿌리, 정제수, 구연산, 비타민C, 젖산칼슘</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2019044604969</t>
+          <t>2019044604975</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>나물인 국내산 우엉채</t>
+          <t>나물인국내산토란대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>젖산칼슘, 비타민C, 구연산, 정제수, 우엉채</t>
+          <t>토란줄기, 정제수, 구연산(무수), 비타민C, 젖산칼슘</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11279,7 +11279,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2019044604972</t>
+          <t>2019044604969</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>나물인국내산배추우거지</t>
+          <t>나물인 국내산 우엉채</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>젖산칼슘, 비타민C, 구연산, 정제수, 배추잎</t>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 우엉채</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11326,7 +11326,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2019044604970</t>
+          <t>2019044604972</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>나물인 국내산연근채</t>
+          <t>나물인국내산배추우거지</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>젖산칼슘, 비타민C, 구연산, 정제수, 연근</t>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 배추잎</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -11373,7 +11373,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2019044604975</t>
+          <t>2019044604970</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>나물인국내산토란대</t>
+          <t>나물인 국내산연근채</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>토란줄기, 정제수, 구연산(무수), 비타민C, 젖산칼슘</t>
+          <t>젖산칼슘, 비타민C, 구연산, 정제수, 연근</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -18611,7 +18611,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>19990623061330</t>
+          <t>19990623061331</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>지리산 케일부추미나리 환</t>
+          <t>지리산홍화인 해국차전자 환</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -18641,12 +18641,12 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>천연후추(흑후추)향, 올리고당, 현미가루, 미나리분말, 케일분말, 부추분말</t>
+          <t>천연후추(흑후추)향, 다시마분말, 올리고당, 볶은현미분말, 느릅나무분말, 창질경이잎, 해국잎</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -18658,7 +18658,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>19990623061331</t>
+          <t>19990623061330</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>지리산홍화인 해국차전자 환</t>
+          <t>지리산 케일부추미나리 환</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -18688,12 +18688,12 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>천연후추(흑후추)향, 다시마분말, 올리고당, 볶은현미분말, 느릅나무분말, 창질경이잎, 해국잎</t>
+          <t>천연후추(흑후추)향, 올리고당, 현미가루, 미나리분말, 케일분말, 부추분말</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -19064,7 +19064,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -19111,7 +19111,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -20350,7 +20350,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2020061604464</t>
+          <t>201904625221237</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20360,32 +20360,32 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>20200616044</t>
+          <t>20190462522</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>애플진저샷</t>
+          <t>리나우 쉐이크</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>채연가</t>
+          <t>주식회사 상상바이오</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>생강, 사과, 레몬, 계피, 오렌지</t>
+          <t>기타가공품, 향료, 비타민C, 곡류가공품, 효소처리스테비아, 기타가공품, 향료, 식물성크림, 쌀단백분말, 망고농축분말, 올리고당, 두류가공품, 엽산, 비타민B2, 혼합제제, 혼합제제, 유함유가공품, 프로바이오틱스(고시형), 판토텐산칼슘, 혼합제제, 산화아연, 혼합제제, 피로인산제이철, 엘라스틴가수분해물, 효모식품, 바나나추출분말, 혼합제제, 과.채가공품, 효모식품, 과.채가공품, 잔탄검, 아라비아검(고시형), 니코틴산아미드, 기타가공품, 기타 식용유지가공품</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -20397,7 +20397,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>20200389748238</t>
+          <t>2020061604464</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20407,44 +20407,44 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>20200389748</t>
+          <t>20200616044</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>산삼진담</t>
+          <t>애플진저샷</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>헬스바이오</t>
+          <t>채연가</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>기타가공품, 홍삼, 침향나무수지가침착된수간목, 산삼배양근추출액, 프락토올리고당</t>
+          <t>생강, 사과, 레몬, 계피, 오렌지</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>20200424149191</t>
+          <t>20200389748238</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -20454,12 +20454,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>20200424149</t>
+          <t>20200389748</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>컴파운드 케이 분말</t>
+          <t>산삼진담</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20469,17 +20469,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>(주)네츄럴굿띵스</t>
+          <t>헬스바이오</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>인삼뿌리분말</t>
+          <t>기타가공품, 홍삼, 침향나무수지가침착된수간목, 산삼배양근추출액, 프락토올리고당</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -20491,7 +20491,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2021029327898</t>
+          <t>20200424149191</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20501,44 +20501,44 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>20210293278</t>
+          <t>20200424149</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>오픈하트 핑크앤화이트 스프링클</t>
+          <t>컴파운드 케이 분말</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>내츄럴팩토리 주식회사</t>
+          <t>(주)네츄럴굿띵스</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>당류가공품, 당류가공품, 당류가공품</t>
+          <t>인삼뿌리분말</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>20220604079140</t>
+          <t>2021029327898</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20548,22 +20548,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>20220604079</t>
+          <t>20210293278</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>해천신골드</t>
+          <t>오픈하트 핑크앤화이트 스프링클</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>(주)원일바이오 제1공장</t>
+          <t>내츄럴팩토리 주식회사</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>칡뿌리, 맥아, 쌀겨, 황금, 삽주뿌리줄기, 맥문동뿌리, 울금덩이뿌리, 엉겅퀴, 모창출뿌리줄기, 감초, 작약뿌리, 천궁뿌리줄기, 계피, 광귤나무열매, 복령균핵, 도라지뿌리, 생강, 참당귀뿌리, 프락토올리고당, 귤나무열매껍질</t>
+          <t>당류가공품, 당류가공품, 당류가공품</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -20585,7 +20585,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>20220520255206</t>
+          <t>20220604079140</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20595,32 +20595,32 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>20220520255</t>
+          <t>20220604079</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>엠오에스(MOS)3</t>
+          <t>해천신골드</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>아인팜</t>
+          <t>(주)원일바이오 제1공장</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>효소식품, 청국장</t>
+          <t>칡뿌리, 맥아, 쌀겨, 황금, 삽주뿌리줄기, 맥문동뿌리, 울금덩이뿌리, 엉겅퀴, 모창출뿌리줄기, 감초, 작약뿌리, 천궁뿌리줄기, 계피, 광귤나무열매, 복령균핵, 도라지뿌리, 생강, 참당귀뿌리, 프락토올리고당, 귤나무열매껍질</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -20632,7 +20632,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>20220520255205</t>
+          <t>20220520255206</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>뿌리장</t>
+          <t>엠오에스(MOS)3</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20667,19 +20667,19 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>볶은현미, 우엉, 둥굴레, 오미자열매, 사양벌꿀, 기타가공품</t>
+          <t>효소식품, 청국장</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>202206834732011</t>
+          <t>20220520255205</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20689,22 +20689,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>20220683473</t>
+          <t>20220520255</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>매스틱 복합추출물</t>
+          <t>뿌리장</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>주식회사 에이브바이오랩스</t>
+          <t>아인팜</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -20714,19 +20714,19 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>식품첨가물, 식품첨가물, 식품첨가물혼합제제, 기타가공품, 효소식품, 식품첨가물, 식품첨가물, 식품첨가물, 기타가공품, 이눌린(고시형), 덱스트린, 식품첨가물, 식품첨가물, 혼합제제, 과.채가공품, 기타가공품, 과.채가공품</t>
+          <t>볶은현미, 우엉, 둥굴레, 오미자열매, 사양벌꿀, 기타가공품</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>202206834732013</t>
+          <t>202206834732011</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>젖산 마그네슘 8중 복합물</t>
+          <t>매스틱 복합추출물</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>유함유가공품, 식품첨가물, 식품첨가물, 식품첨가물, 올리고당, 포도당, 이눌린/치커리추출물(고시형), 식품첨가물, 혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 식품첨가물</t>
+          <t>식품첨가물, 식품첨가물, 식품첨가물혼합제제, 기타가공품, 효소식품, 식품첨가물, 식품첨가물, 식품첨가물, 기타가공품, 이눌린(고시형), 덱스트린, 식품첨가물, 식품첨가물, 혼합제제, 과.채가공품, 기타가공품, 과.채가공품</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -20773,7 +20773,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>202206834731993</t>
+          <t>202206834732013</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>조인트 밸런스 복합물</t>
+          <t>젖산 마그네슘 8중 복합물</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20808,19 +20808,19 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>기타 수산물가공품, 기타가공품, 기타가공품, 기타 농산가공품, NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 식품첨가물, 식품첨가물혼합제제, 뮤코다당.단백(고시형), 식품첨가물, 고형차, 식품첨가물, 식품첨가물, 기타가공품, 올리고당, 식품첨가물, 덱스트린, 이눌린/치커리추출물(고시형)</t>
+          <t>유함유가공품, 식품첨가물, 식품첨가물, 식품첨가물, 올리고당, 포도당, 이눌린/치커리추출물(고시형), 식품첨가물, 혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 식품첨가물</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>202206834732007</t>
+          <t>202206834731993</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20835,7 +20835,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>젖산마그네슘 밸런스 컴플렉스</t>
+          <t>조인트 밸런스 복합물</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -20855,19 +20855,19 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>식품첨가물, 식품첨가물, 이눌린/치커리추출물(고시형), 당류가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
+          <t>기타 수산물가공품, 기타가공품, 기타가공품, 기타 농산가공품, NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 식품첨가물, 식품첨가물혼합제제, 뮤코다당.단백(고시형), 식품첨가물, 고형차, 식품첨가물, 식품첨가물, 기타가공품, 올리고당, 식품첨가물, 덱스트린, 이눌린/치커리추출물(고시형)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>관절</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>202206834732009</t>
+          <t>202206834732007</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20882,7 +20882,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>매스틱 혼합추출물</t>
+          <t>젖산마그네슘 밸런스 컴플렉스</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -20902,7 +20902,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>기타가공품, 과.채가공품, 혼합제제, 식품첨가물, 식품첨가물, 덱스트린, 이눌린(고시형), 기타가공품, 효소식품, 기타가공품, 과.채가공품, 식품첨가물, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
+          <t>식품첨가물, 식품첨가물, 이눌린/치커리추출물(고시형), 당류가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -20914,7 +20914,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>202206834732015</t>
+          <t>202206834732009</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>매스틱밸런스포뮬러</t>
+          <t>매스틱 혼합추출물</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -20949,7 +20949,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>기타가공품, 효소식품, 혼합제제, 과.채가공품, 식품첨가물, 덱스트린, 포도당, 이눌린(고시형), 식품첨가물, 식품첨가물혼합제제</t>
+          <t>기타가공품, 과.채가공품, 혼합제제, 식품첨가물, 식품첨가물, 덱스트린, 이눌린(고시형), 기타가공품, 효소식품, 기타가공품, 과.채가공품, 식품첨가물, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -20961,7 +20961,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>202202738571324</t>
+          <t>202206834732015</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20971,22 +20971,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>20220273857</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>발효 복분자 복합분말</t>
+          <t>매스틱밸런스포뮬러</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>(주)네이처코퍼레이션</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -20996,12 +20996,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>과.채가공품, 기타가공품, 서류가공품, 과.채가공품, 기타가공품, 유산균, 비타민C, 이산화규소</t>
+          <t>기타가공품, 효소식품, 혼합제제, 과.채가공품, 식품첨가물, 덱스트린, 포도당, 이눌린(고시형), 식품첨가물, 식품첨가물혼합제제</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -21055,7 +21055,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>20230268165166</t>
+          <t>202202738571324</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -21065,12 +21065,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>20230268165</t>
+          <t>20220273857</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>G-아그작 크런치 파우더</t>
+          <t>발효 복분자 복합분말</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -21080,29 +21080,29 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>그린스퀘어(주)</t>
+          <t>(주)네이처코퍼레이션</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>곡류가공품, 곡류가공품</t>
+          <t>과.채가공품, 기타가공품, 서류가공품, 과.채가공품, 기타가공품, 유산균, 비타민C, 이산화규소</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>20230268165165</t>
+          <t>20230268165166</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>G-지스타 크리스피 파우더</t>
+          <t>G-아그작 크런치 파우더</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>감자플레이크, 곡류가공품</t>
+          <t>곡류가공품, 곡류가공품</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -21149,7 +21149,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>20230528144366</t>
+          <t>20230268165165</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21159,12 +21159,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20230268165</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>올인원 포뮬러 6 [콜라겐 글루타치온 히알루론산 S]</t>
+          <t>G-지스타 크리스피 파우더</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -21174,29 +21174,29 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>그린스퀘어(주)</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>비타민C, 레몬과즙분말, L-프롤린, 건조효모, 생선콜라겐분말, 자일리톨, 포도당, DL-사과산, 이산화규소, 산화아연, 효소처리스테비아, 레몬향분말, 히알루론산혼합제제, 프락토올리고당</t>
+          <t>감자플레이크, 곡류가공품</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>20230528144362</t>
+          <t>20230528144366</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>콜린 미오이노시톨 4000</t>
+          <t>올인원 포뮬러 6 [콜라겐 글루타치온 히알루론산 S]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -21231,19 +21231,19 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>건조효모(비타민D), 주석산수소콜린, α-시클로덱스트린, 유산균혼합분말, 비타민B2, 비타민B1염산염, 비타민B6염산염, 분말비타민B12혼합제제, 레몬껍질추출물분말, 자몽추출분말, 비타민E혼합제제, 구연산(무수), 효소처리스테비아, 캐롭분말, 라즈베리향분말, DL-사과산, 비타민C, 산화마그네슘, 치커리추출분말, 이노시톨</t>
+          <t>비타민C, 레몬과즙분말, L-프롤린, 건조효모, 생선콜라겐분말, 자일리톨, 포도당, DL-사과산, 이산화규소, 산화아연, 효소처리스테비아, 레몬향분말, 히알루론산혼합제제, 프락토올리고당</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>여성건강</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>20230431741101</t>
+          <t>20230528144362</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21253,22 +21253,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>20230431741</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>수박착즙액</t>
+          <t>콜린 미오이노시톨 4000</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>(주)즙스토리</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -21278,19 +21278,19 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>수박열매</t>
+          <t>건조효모(비타민D), 주석산수소콜린, α-시클로덱스트린, 유산균혼합분말, 비타민B2, 비타민B1염산염, 비타민B6염산염, 분말비타민B12혼합제제, 레몬껍질추출물분말, 자몽추출분말, 비타민E혼합제제, 구연산(무수), 효소처리스테비아, 캐롭분말, 라즈베리향분말, DL-사과산, 비타민C, 산화마그네슘, 치커리추출분말, 이노시톨</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>여성건강</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>20230609874616</t>
+          <t>20230431741101</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21300,12 +21300,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>20230609874</t>
+          <t>20230431741</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>리포좀 식물성멜라토닌 함유 멜라나잇</t>
+          <t>수박착즙액</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -21315,29 +21315,29 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>(주)뉴트리션바이오</t>
+          <t>(주)즙스토리</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>기타 농산가공품, 레몬밤분말, 기타가공품, 기타가공품, 식품첨가물, 기타 농산가공품, 기타가공품, L-트립토판, 기타가공품, 유함유가공품, 해조혼합분말, 산화마그네슘, 포도당, 과.채가공품, L-테아닌(고시형), L-시스틴, 효모식품, 효모식품</t>
+          <t>수박열매</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>20230609874615</t>
+          <t>20230609874616</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21352,7 +21352,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>그린 아세로라C 밸런스정</t>
+          <t>리포좀 식물성멜라토닌 함유 멜라나잇</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -21372,19 +21372,19 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>스테아린산마그네슘, 기타가공품</t>
+          <t>기타 농산가공품, 레몬밤분말, 기타가공품, 기타가공품, 식품첨가물, 기타 농산가공품, 기타가공품, L-트립토판, 기타가공품, 유함유가공품, 해조혼합분말, 산화마그네슘, 포도당, 과.채가공품, L-테아닌(고시형), L-시스틴, 효모식품, 효모식품</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>20240661119130</t>
+          <t>20230609874615</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21394,22 +21394,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>20240661119</t>
+          <t>20230609874</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>퓨어젠 A2 양유단백질</t>
+          <t>그린 아세로라C 밸런스정</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>주식회사 뉴트리플래닛</t>
+          <t>(주)뉴트리션바이오</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -21419,19 +21419,19 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>탈지분유</t>
+          <t>스테아린산마그네슘, 기타가공품</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2024094504854</t>
+          <t>20240661119130</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21441,12 +21441,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>20240945048</t>
+          <t>20240661119</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>뿌리한입 도라지 분말유산균</t>
+          <t>퓨어젠 A2 양유단백질</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>경남약용작물산업화지원센터</t>
+          <t>주식회사 뉴트리플래닛</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -21466,19 +21466,19 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>유산균혼합분말, 도라지뿌리, 레몬과즙분말, 포도당, 레몬향분말, 구연산(무수)</t>
+          <t>탈지분유</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2024057732133</t>
+          <t>2024094504854</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21488,44 +21488,44 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>20240577321</t>
+          <t>20240945048</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>절단감자</t>
+          <t>뿌리한입 도라지 분말유산균</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>농업회사 한신식품</t>
+          <t>경남약용작물산업화지원센터</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>감자</t>
+          <t>유산균혼합분말, 도라지뿌리, 레몬과즙분말, 포도당, 레몬향분말, 구연산(무수)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>202506580412</t>
+          <t>2024057732133</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21535,32 +21535,32 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>20250658041</t>
+          <t>20240577321</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>땅콩빵쌀보리 다목적 프리믹스</t>
+          <t>절단감자</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>주식회사 세화식품</t>
+          <t>농업회사 한신식품</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>합성향료, 잔탄검, 탄산수소나트륨, 정제소금, 변성전분, 변성전분, 변성전분, 보리가루, 쌀가루, 백설탕</t>
+          <t>감자</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -21572,42 +21572,42 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>19830464033570</t>
+          <t>202506580412</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>19830464033</t>
+          <t>20250658041</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>이디야 깊고 진한 율무차</t>
+          <t>땅콩빵쌀보리 다목적 프리믹스</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>(주)오뚜기</t>
+          <t>주식회사 세화식품</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>설탕, 식물성크림, 통밀, 대두분, 아몬드, 기타가공품, 알파미분, 율무분말, 찰옥수수전분, 호두, 잣, 정제소금, 이산화규소, 땅콩향</t>
+          <t>합성향료, 잔탄검, 탄산수소나트륨, 정제소금, 변성전분, 변성전분, 변성전분, 보리가루, 쌀가루, 백설탕</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -21619,7 +21619,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>19830464033569</t>
+          <t>19830464033570</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>이디야 깊고 진한 쌍화차</t>
+          <t>이디야 깊고 진한 율무차</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -21649,12 +21649,12 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>정제소금, 이산화규소, 기타가공품, 덱스트린, 설탕, 대추채, 아몬드, 잣</t>
+          <t>설탕, 식물성크림, 통밀, 대두분, 아몬드, 기타가공품, 알파미분, 율무분말, 찰옥수수전분, 호두, 잣, 정제소금, 이산화규소, 땅콩향</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -21666,7 +21666,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>198604350131766</t>
+          <t>19830464033569</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21676,44 +21676,44 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>19860435013</t>
+          <t>19830464033</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>여에스더 리포좀 NMN 부스터</t>
+          <t>이디야 깊고 진한 쌍화차</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>코스맥스바이오(주)</t>
+          <t>(주)오뚜기</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>정제수, 알룰로오스, 에리스리톨, 로커스트콩검, 식용색소적색제40호, 니코틴산아미드, 머스켓향, 구연산, 구연산삼나트륨, 효모, 효소처리스테비아, 믹스베리향, DL-사과산, 카라기난혼합제제, 베타인, 황금추출물, 포도농축액, 베리혼합농축액, 비타민 A 혼합제제, 비타민E혼합제제, 비타민B6염산염, 비타민D3혼합제제, 비타민B12, 혼합제제</t>
+          <t>정제소금, 이산화규소, 기타가공품, 덱스트린, 설탕, 대추채, 아몬드, 잣</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>199401994801404</t>
+          <t>198604350131766</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21723,44 +21723,44 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>19940199480</t>
+          <t>19860435013</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>바닐라 분말향 #14</t>
+          <t>여에스더 리포좀 NMN 부스터</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>서울향료(주)</t>
+          <t>코스맥스바이오(주)</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>포도당, 포도당, 합성향료(Vanillin)</t>
+          <t>정제수, 알룰로오스, 에리스리톨, 로커스트콩검, 식용색소적색제40호, 니코틴산아미드, 머스켓향, 구연산, 구연산삼나트륨, 효모, 효소처리스테비아, 믹스베리향, DL-사과산, 카라기난혼합제제, 베타인, 황금추출물, 포도농축액, 베리혼합농축액, 비타민 A 혼합제제, 비타민E혼합제제, 비타민B6염산염, 비타민D3혼합제제, 비타민B12, 혼합제제</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>199704451445045</t>
+          <t>199401994801404</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21770,12 +21770,12 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>19970445144</t>
+          <t>19940199480</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>호박카스테라크림빵용크림</t>
+          <t>바닐라 분말향 #14</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>씨제이푸드빌주식회사</t>
+          <t>서울향료(주)</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>ε-폴리리신, 기타가공품, 변성전분, 우유, 기타가공품, 난황액, 설탕, 마가린, 전분, 밀가루</t>
+          <t>포도당, 포도당, 합성향료(Vanillin)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -21807,7 +21807,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>200104450021126</t>
+          <t>199704451445045</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21817,12 +21817,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>20010445002</t>
+          <t>19970445144</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>단백질쉐이크 플레인</t>
+          <t>호박카스테라크림빵용크림</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>엠에스바이오텍(주)</t>
+          <t>씨제이푸드빌주식회사</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -21842,19 +21842,19 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>유청단백분말, L-글루타민, 효모식품, 비타민C, 기타가공품, 기타가공품, 기타가공품, 정제소금, 이산화규소, 글루콘산마그네슘, 구아검, 차전자피식이섬유(고시형), 이노시톨, 옥수수전분, L-아르지닌, L-로이신, 건조효모(크롬함유), 나한과추출물분말, 치아씨앗, 기타가공품, 난소화성말토덱스트린(고시형), 탈지분유, 향료, 두류가공품, 알룰로오스, 치커리식이섬유, 분리대두단백, 분리유단백</t>
+          <t>ε-폴리리신, 기타가공품, 변성전분, 우유, 기타가공품, 난황액, 설탕, 마가린, 전분, 밀가루</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>200303950191041</t>
+          <t>200104450021126</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21864,22 +21864,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>20030395019</t>
+          <t>20010445002</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>푸룬BCAA</t>
+          <t>단백질쉐이크 플레인</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>(주)유유헬스케어</t>
+          <t>엠에스바이오텍(주)</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -21889,19 +21889,19 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>혼합제제, 정제수, 서양자두열매착즙액</t>
+          <t>유청단백분말, L-글루타민, 효모식품, 비타민C, 기타가공품, 기타가공품, 기타가공품, 정제소금, 이산화규소, 글루콘산마그네슘, 구아검, 차전자피식이섬유(고시형), 이노시톨, 옥수수전분, L-아르지닌, L-로이신, 건조효모(크롬함유), 나한과추출물분말, 치아씨앗, 기타가공품, 난소화성말토덱스트린(고시형), 탈지분유, 향료, 두류가공품, 알룰로오스, 치커리식이섬유, 분리대두단백, 분리유단백</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>남성건강</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>200303950191039</t>
+          <t>200303950191041</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21916,7 +21916,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>푸룬오르조젤리</t>
+          <t>푸룬BCAA</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -21936,19 +21936,19 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>혼합제제, 구연산(무수), 효소처리스테비아, 보리, 난소화성말토덱스트린(고시형), 정제수, 서양자두열매착즙액</t>
+          <t>혼합제제, 정제수, 서양자두열매착즙액</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>남성건강</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>200303950191038</t>
+          <t>200303950191039</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21963,12 +21963,12 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>키즈칼마디</t>
+          <t>푸룬오르조젤리</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -21983,19 +21983,19 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>포도향분말, 구연산(무수), 효소처리스테비아, 혼합제제, 프락토올리고당, 포도농축액분말, 유청단백분말, 산양유분말, 한속단추출분말, 초유단백분말, 비타민D3혼합제제, 글루콘산마그네슘, 구연산칼슘, 정제수</t>
+          <t>혼합제제, 구연산(무수), 효소처리스테비아, 보리, 난소화성말토덱스트린(고시형), 정제수, 서양자두열매착즙액</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>20070435069986</t>
+          <t>200303950191038</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22005,22 +22005,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>20070435069</t>
+          <t>20030395019</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>태을 순맥</t>
+          <t>키즈칼마디</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>농업법인(주)옻가네</t>
+          <t>(주)유유헬스케어</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -22030,19 +22030,19 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>정제수, 액상차</t>
+          <t>포도향분말, 구연산(무수), 효소처리스테비아, 혼합제제, 프락토올리고당, 포도농축액분말, 유청단백분말, 산양유분말, 한속단추출분말, 초유단백분말, 비타민D3혼합제제, 글루콘산마그네슘, 구연산칼슘, 정제수</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>20080415099398</t>
+          <t>20070435069986</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22052,22 +22052,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>20080415099</t>
+          <t>20070435069</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>휴럼 요거베리 상온발효 카스피 그릭요거트 스타터</t>
+          <t>태을 순맥</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>주식회사 휴럼</t>
+          <t>농업법인(주)옻가네</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -22077,12 +22077,12 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>당류가공품, 유당, 전지분유, 분말결정포도당, 유산균, 분리유단백분말, 유산균, 치커리뿌리추출물분말, 유산균</t>
+          <t>정제수, 액상차</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -22119,7 +22119,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -22136,7 +22136,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>20090624059790</t>
+          <t>20080415099398</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22146,44 +22146,44 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>20090624059</t>
+          <t>20080415099</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>석류착즙혼합액</t>
+          <t>휴럼 요거베리 상온발효 카스피 그릭요거트 스타터</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>농업회사법인(주)힐링팜</t>
+          <t>주식회사 휴럼</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>프락토올리고당, 석류착즙액</t>
+          <t>당류가공품, 유당, 전지분유, 분말결정포도당, 유산균, 분리유단백분말, 유산균, 치커리뿌리추출물분말, 유산균</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>20100614388722</t>
+          <t>20090624059790</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22193,44 +22193,44 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>20100614388</t>
+          <t>20090624059</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>루솔 과채플랜 엘더베리&amp;양배추</t>
+          <t>석류착즙혼합액</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>(주)천호엔케어</t>
+          <t>농업회사법인(주)힐링팜</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>글루콘산아연, 효소처리스테비아, DL-사과산, 블루베리농축액, 과.채가공품, 열처리블랙엘더베리열매농축액, 사과농축액, 정제수</t>
+          <t>프락토올리고당, 석류착즙액</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>20100614388716</t>
+          <t>20100614388722</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>루솔 과채플랜 빌베리&amp;토마토</t>
+          <t>루솔 과채플랜 엘더베리&amp;양배추</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -22265,19 +22265,19 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>효소처리스테비아, 구연산(무수), 사과농축액, 정제수, 토마토농축액, 미르틸루스산앵도열매농축액, 파인애플농축액</t>
+          <t>글루콘산아연, 효소처리스테비아, DL-사과산, 블루베리농축액, 과.채가공품, 열처리블랙엘더베리열매농축액, 사과농축액, 정제수</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>201504420251392</t>
+          <t>20100614388716</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -22287,22 +22287,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>20150442025</t>
+          <t>20100614388</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>약도라지농축액</t>
+          <t>루솔 과채플랜 빌베리&amp;토마토</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>주식회사 하람</t>
+          <t>(주)천호엔케어</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -22312,19 +22312,19 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>도라지뿌리</t>
+          <t>효소처리스테비아, 구연산(무수), 사과농축액, 정제수, 토마토농축액, 미르틸루스산앵도열매농축액, 파인애플농축액</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>20150481214138</t>
+          <t>201504420251392</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22334,44 +22334,44 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>20150481214</t>
+          <t>20150442025</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>베르베린 밀크씨슬 포뮬러 MAX</t>
+          <t>약도라지농축액</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>(주)케비젠</t>
+          <t>주식회사 하람</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>기타가공품, 스테아린산마그네슘, 기타가공품, 레드비트주스분말, 기타가공품, 기타가공품, 이노시톨, 여주추출분말, 이산화규소, 카복시메틸셀룰로스칼슘, 해조칼슘, 결정셀룰로스, 밀크씨슬추출물, 과.채가공품, 난소화성말토덱스트린(고시형)</t>
+          <t>도라지뿌리</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2016051216182</t>
+          <t>20150481214138</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22381,44 +22381,44 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>20160512161</t>
+          <t>20150481214</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>나주 배도라지즙</t>
+          <t>베르베린 밀크씨슬 포뮬러 MAX</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>나주시천연색소산업화지원센터</t>
+          <t>(주)케비젠</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>도라지뿌리농축액, 배착즙액</t>
+          <t>기타가공품, 스테아린산마그네슘, 기타가공품, 레드비트주스분말, 기타가공품, 기타가공품, 이노시톨, 여주추출분말, 이산화규소, 카복시메틸셀룰로스칼슘, 해조칼슘, 결정셀룰로스, 밀크씨슬추출물, 과.채가공품, 난소화성말토덱스트린(고시형)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>20170449014375</t>
+          <t>2016051216182</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22428,44 +22428,44 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>20170449014</t>
+          <t>20160512161</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>갈랑가추출분말</t>
+          <t>나주 배도라지즙</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>(주)미전코리아</t>
+          <t>나주시천연색소산업화지원센터</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>덱스트린, 과.채가공품</t>
+          <t>도라지뿌리농축액, 배착즙액</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>20180042370328</t>
+          <t>20170449014375</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22475,12 +22475,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>20180042370</t>
+          <t>20170449014</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>황금 커큐민</t>
+          <t>갈랑가추출분말</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -22490,29 +22490,29 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>유한네이처</t>
+          <t>(주)미전코리아</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>정제수, 후추열매, 감귤껍질, 맥아, 마뿌리, 강황뿌리줄기</t>
+          <t>덱스트린, 과.채가공품</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>20180042928136</t>
+          <t>20180042370328</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22522,44 +22522,44 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>20180042928</t>
+          <t>20180042370</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>자스민그린말차</t>
+          <t>황금 커큐민</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>(주)우리꽃연구소</t>
+          <t>유한네이처</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>정제소금, 고형차, 효소처리스테비아, 향료, 침출차, 침출차, 정제수, 알룰로오스</t>
+          <t>정제수, 후추열매, 감귤껍질, 맥아, 마뿌리, 강황뿌리줄기</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>20190349087120</t>
+          <t>20180042928136</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22569,32 +22569,32 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>20190349087</t>
+          <t>20180042928</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>본연재</t>
+          <t>자스민그린말차</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>투더</t>
+          <t>(주)우리꽃연구소</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>누룩, 무씨앗, 대추, 삼씨앗, 강황뿌리줄기, 감초</t>
+          <t>정제소금, 고형차, 효소처리스테비아, 향료, 침출차, 침출차, 정제수, 알룰로오스</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -22606,7 +22606,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>20190349087121</t>
+          <t>20190349087120</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>자연결</t>
+          <t>본연재</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -22636,12 +22636,12 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>마가목열매, 헛개나무열매, 참당귀뿌리, 천궁뿌리줄기, 뽕나무잎, 연잎</t>
+          <t>누룩, 무씨앗, 대추, 삼씨앗, 강황뿌리줄기, 감초</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>201904625221240</t>
+          <t>20190349087121</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -22663,32 +22663,32 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>20190462522</t>
+          <t>20190349087</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>옥수수수염호박복합물</t>
+          <t>자연결</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>주식회사 상상바이오</t>
+          <t>투더</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>옥수수수염추출분말, 옥수수수염추출분말, 설탕, 과.채가공품, 고형차, 기타가공품</t>
+          <t>마가목열매, 헛개나무열매, 참당귀뿌리, 천궁뿌리줄기, 뽕나무잎, 연잎</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -22700,7 +22700,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2020053208585</t>
+          <t>201904625221240</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -22710,32 +22710,32 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>20200532085</t>
+          <t>20190462522</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>야채박사 오렌지</t>
+          <t>옥수수수염호박복합물</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>아이비씨영농조합법인</t>
+          <t>주식회사 상상바이오</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>오렌지</t>
+          <t>옥수수수염추출분말, 옥수수수염추출분말, 설탕, 과.채가공품, 고형차, 기타가공품</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -22747,7 +22747,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2020053208584</t>
+          <t>201904625221243</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -22757,32 +22757,32 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>20200532085</t>
+          <t>20190462522</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>야채박사 키위</t>
+          <t>포도씨생강천궁복합물</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>아이비씨영농조합법인</t>
+          <t>주식회사 상상바이오</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>키위열매</t>
+          <t>과.채가공품, 기타가공품, 기타가공품, 과.채가공품, 설탕</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -22794,7 +22794,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>20200363209351</t>
+          <t>201904625221242</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -22804,12 +22804,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>20200363209</t>
+          <t>20190462522</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>딸기콩포트B</t>
+          <t>비타민B미네랄복합물</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -22819,29 +22819,29 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>(주)누리지에프에스</t>
+          <t>주식회사 상상바이오</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>엽산, 판토텐산칼슘, 기타가공품, 혼합제제, 탄산마그네슘, 혼합제제, 피로인산제이철, 비타민B2, 혼합제제, 아세로라농축분말, 비타민B1염산염, 사과농축분말</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2022064807732</t>
+          <t>2020053208585</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -22851,12 +22851,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>20220648077</t>
+          <t>20200532085</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>블랙 스테비아 대추방울토마토 망고향</t>
+          <t>야채박사 오렌지</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -22866,17 +22866,17 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>농업회사법인 엔에프지 주식회사</t>
+          <t>아이비씨영농조합법인</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>스테비올배당체, 나무토마토열매, 정제수, 수크랄로스, ε-폴리리신, 향료</t>
+          <t>오렌지</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -22888,7 +22888,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2022064807733</t>
+          <t>2020053208584</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -22898,12 +22898,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>20220648077</t>
+          <t>20200532085</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>스테비아 대추방울토마토 망고향</t>
+          <t>야채박사 키위</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -22913,17 +22913,17 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>농업회사법인 엔에프지 주식회사</t>
+          <t>아이비씨영농조합법인</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>수크랄로스, ε-폴리리신, 향료, 스테비올배당체, 정제수, 나무토마토열매</t>
+          <t>키위열매</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -22935,7 +22935,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>202206834731877</t>
+          <t>20200363209351</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -22945,32 +22945,32 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>20220683473</t>
+          <t>20200363209</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 버닝 정</t>
+          <t>딸기콩포트B</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>주식회사 에이브바이오랩스</t>
+          <t>(주)누리지에프에스</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물, 식품첨가물</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -22982,7 +22982,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>202206834731875</t>
+          <t>2022064807732</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -22992,32 +22992,32 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>20220683473</t>
+          <t>20220648077</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>이너도르 데오잇</t>
+          <t>블랙 스테비아 대추방울토마토 망고향</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>주식회사 에이브바이오랩스</t>
+          <t>농업회사법인 엔에프지 주식회사</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>이눌린/치커리추출물(고시형), 덱스트린, 과.채가공품, 기타가공품, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 기타가공품, 식품첨가물</t>
+          <t>스테비올배당체, 나무토마토열매, 정제수, 수크랄로스, ε-폴리리신, 향료</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -23029,7 +23029,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>202202738571327</t>
+          <t>2022064807733</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -23039,32 +23039,32 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>20220273857</t>
+          <t>20220648077</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 버닝 마스터</t>
+          <t>스테비아 대추방울토마토 망고향</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>(주)네이처코퍼레이션</t>
+          <t>농업회사법인 엔에프지 주식회사</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>기타가공품, 스테아린산마그네슘</t>
+          <t>수크랄로스, ε-폴리리신, 향료, 스테비올배당체, 정제수, 나무토마토열매</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -23076,7 +23076,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>202202738571326</t>
+          <t>202206834731877</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -23086,22 +23086,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>20220273857</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>뉴 파라다이스 그레인 분말</t>
+          <t>파라다이스 그레인 버닝 정</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>(주)네이처코퍼레이션</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -23111,19 +23111,19 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>기타가공품, 과.채가공품, 이산화규소, 효소식품, α-시클로덱스트린, 기타가공품, 기타가공품, 기타가공품, 포도당, 기타 농산가공품, 기타가공품</t>
+          <t>고형차, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>다이어트</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>20230528144369</t>
+          <t>202206834731875</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -23133,22 +23133,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>쌀 발효 양태반 플라센타 프라임</t>
+          <t>이너도르 데오잇</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -23158,7 +23158,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>이눌린/치커리추출물(고시형), 덱스트린, 과.채가공품, 기타가공품, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 기타가공품, 식품첨가물</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -23170,7 +23170,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>20230528144368</t>
+          <t>202202738571327</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -23180,44 +23180,44 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20220273857</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>쌀 발효 양태반 복합물</t>
+          <t>파라다이스 그레인 버닝 마스터</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>(주)네이처코퍼레이션</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>구연산(무수), 오렌지맛분말, 드링크향, 오렌지과즙분말, 파인애플맛분말, 양태반분말, 파인애플주스분말, 자일리톨, 포도당, L-시스틴, L-아르지닌, 쌀발효분말, DL-사과산, 이산화규소, 녹용분말, 침향나무수지가침착된수간목분말, 영지버섯자실체추출분말, 산화아연, 비타민B6염산염, 비타민B2, 비타민B1염산염</t>
+          <t>기타가공품, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>20230528144367</t>
+          <t>202202738571326</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -23227,12 +23227,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20220273857</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>파워 마그네슘</t>
+          <t>뉴 파라다이스 그레인 분말</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -23242,29 +23242,29 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>(주)네이처코퍼레이션</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>파인애플향분말, 파인애플농축, 글루콘산마그네슘, 자일리톨, 포도당, DL-사과산, 효소처리스테비아, L-젖산마그네슘, 구연산(무수), 이산화규소, 파인애플맛분말</t>
+          <t>기타가공품, 과.채가공품, 이산화규소, 효소식품, α-시클로덱스트린, 기타가공품, 기타가공품, 기타가공품, 포도당, 기타 농산가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>다이어트</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>20230612332357</t>
+          <t>20230528144369</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>20230612332</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>꽃송이칸</t>
+          <t>쌀 발효 양태반 플라센타 프라임</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>(주)웰레스트</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>꽃송이버섯분말, 덱스트린, 치커리뿌리추출물분말, 곡류가공품, 귀리식이섬유, 병풀추출, 볶은현미, 고형차, 효모식품, 대나무수액, 인절미향</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -23311,7 +23311,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2023080138111</t>
+          <t>20230528144368</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -23321,12 +23321,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>20230801381</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>셀로커브</t>
+          <t>쌀 발효 양태반 복합물</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>영농조합법인 금강농산</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -23346,19 +23346,19 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>건조팽이버섯분말, 구아검가수분해물(고시형), 트레할로스, 이눌린분말, 난소화성말토덱스트린분말(고시형)</t>
+          <t>구연산(무수), 오렌지맛분말, 드링크향, 오렌지과즙분말, 파인애플맛분말, 양태반분말, 파인애플주스분말, 자일리톨, 포도당, L-시스틴, L-아르지닌, 쌀발효분말, DL-사과산, 이산화규소, 녹용분말, 침향나무수지가침착된수간목분말, 영지버섯자실체추출분말, 산화아연, 비타민B6염산염, 비타민B2, 비타민B1염산염</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>202605853077</t>
+          <t>20230528144367</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -23368,12 +23368,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>20260585307</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>꿀요거트볼</t>
+          <t>파워 마그네슘</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>우리웰푸드 농업회사법인 주식회사</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>농후발효유, 사양벌꿀</t>
+          <t>파인애플향분말, 파인애플농축, 글루콘산마그네슘, 자일리톨, 포도당, DL-사과산, 효소처리스테비아, L-젖산마그네슘, 구연산(무수), 이산화규소, 파인애플맛분말</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -23405,45 +23405,186 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
+          <t>20230612332357</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>20230612332</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>꽃송이칸</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>(주)웰레스트</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>꽃송이버섯분말, 덱스트린, 치커리뿌리추출물분말, 곡류가공품, 귀리식이섬유, 병풀추출, 볶은현미, 고형차, 효모식품, 대나무수액, 인절미향</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2023080138111</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>20230801381</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>셀로커브</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>영농조합법인 금강농산</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>건조팽이버섯분말, 구아검가수분해물(고시형), 트레할로스, 이눌린분말, 난소화성말토덱스트린분말(고시형)</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>202605853077</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>20260585307</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>꿀요거트볼</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>우리웰푸드 농업회사법인 주식회사</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>농후발효유, 사양벌꿀</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
           <t>20230609874620</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>20261008</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
+      <c r="C312" t="inlineStr">
         <is>
           <t>20230609874</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
+      <c r="D312" t="inlineStr">
         <is>
           <t>프리미엄 참좋은 크랜베리</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
+      <c r="E312" t="inlineStr">
         <is>
           <t>과.채가공품</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
+      <c r="F312" t="inlineStr">
         <is>
           <t>(주)뉴트리션바이오</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
         <is>
           <t>기타가공품, 스테아린산마그네슘, 이산화규소, 산화아연, D-만노오스, 비타민B6염산염, 과.채가공품, 과.채가공품, 과.채가공품</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr">
+      <c r="I312" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
@@ -26653,7 +26794,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -26692,10 +26833,10 @@
         <v>7</v>
       </c>
       <c r="S47" s="10" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="T47" s="8" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48">
@@ -26717,7 +26858,7 @@
         <v>-33</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>-92</v>
+        <v>-91</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>-1</v>
@@ -26756,10 +26897,10 @@
         <v>-56</v>
       </c>
       <c r="S48" s="12" t="n">
-        <v>-824</v>
+        <v>-822</v>
       </c>
       <c r="T48" s="12" t="n">
-        <v>-1308</v>
+        <v>-1305</v>
       </c>
     </row>
     <row r="49">
@@ -26845,7 +26986,7 @@
         <v>-1</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>0</v>
@@ -26884,10 +27025,10 @@
         <v>-7</v>
       </c>
       <c r="S50" s="12" t="n">
-        <v>-188</v>
+        <v>-190</v>
       </c>
       <c r="T50" s="12" t="n">
-        <v>-308</v>
+        <v>-311</v>
       </c>
     </row>
     <row r="51">

--- a/output/2026-10_품목신고보고현황.xlsx
+++ b/output/2026-10_품목신고보고현황.xlsx
@@ -8912,7 +8912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I352"/>
+  <dimension ref="A1:I356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -10574,7 +10574,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20140612266131</t>
+          <t>20140612266132</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>지니라이프 녹용홍삼스틱眞</t>
+          <t>식물혼합농축액GL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -10604,24 +10604,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>녹용추출액, 식물혼합농축액, 덱스트린, 물엿, 홍삼농축액, 구연산(무수), 비타민C, 타우린, 잔탄검</t>
+          <t>감초, 불로초자실체, 복령균핵, 황기, 삽주뿌리줄기박, 천궁뿌리줄기, 약쑥잎, 지황포제가공한뿌리, 구절초, 참당귀, 칡뿌리, 대추, 익모초지상부, 사철쑥, 물엿, 정제수</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20140612266132</t>
+          <t>20140612266131</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>식물혼합농축액GL</t>
+          <t>지니라이프 녹용홍삼스틱眞</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -10651,17 +10651,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>감초, 불로초자실체, 복령균핵, 황기, 삽주뿌리줄기박, 천궁뿌리줄기, 약쑥잎, 지황포제가공한뿌리, 구절초, 참당귀, 칡뿌리, 대추, 익모초지상부, 사철쑥, 물엿, 정제수</t>
+          <t>녹용추출액, 식물혼합농축액, 덱스트린, 물엿, 홍삼농축액, 구연산(무수), 비타민C, 타우린, 잔탄검</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
@@ -20491,7 +20491,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>20200389748238</t>
+          <t>20200451073175</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20501,44 +20501,44 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>20200389748</t>
+          <t>20200451073</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>산삼진담</t>
+          <t>들애지음 여주분말</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>헬스바이오</t>
+          <t>괴산군농산물가공협동조합</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>기타가공품, 홍삼, 침향나무수지가침착된수간목, 산삼배양근추출액, 프락토올리고당</t>
+          <t>여주</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>20200424149191</t>
+          <t>20200389748238</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20548,12 +20548,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>20200424149</t>
+          <t>20200389748</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>컴파운드 케이 분말</t>
+          <t>산삼진담</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20563,17 +20563,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>(주)네츄럴굿띵스</t>
+          <t>헬스바이오</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>인삼뿌리분말</t>
+          <t>기타가공품, 홍삼, 침향나무수지가침착된수간목, 산삼배양근추출액, 프락토올리고당</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -20585,7 +20585,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2021029327898</t>
+          <t>20200424149191</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20595,44 +20595,44 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>20210293278</t>
+          <t>20200424149</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>오픈하트 핑크앤화이트 스프링클</t>
+          <t>컴파운드 케이 분말</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>내츄럴팩토리 주식회사</t>
+          <t>(주)네츄럴굿띵스</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>당류가공품, 당류가공품, 당류가공품</t>
+          <t>인삼뿌리분말</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>20220604079140</t>
+          <t>2021029327898</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>20220604079</t>
+          <t>20210293278</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>해천신골드</t>
+          <t>오픈하트 핑크앤화이트 스프링클</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>(주)원일바이오 제1공장</t>
+          <t>내츄럴팩토리 주식회사</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>칡뿌리, 맥아, 쌀겨, 황금, 삽주뿌리줄기, 맥문동뿌리, 울금덩이뿌리, 엉겅퀴, 모창출뿌리줄기, 감초, 작약뿌리, 천궁뿌리줄기, 계피, 광귤나무열매, 복령균핵, 도라지뿌리, 생강, 참당귀뿌리, 프락토올리고당, 귤나무열매껍질</t>
+          <t>당류가공품, 당류가공품, 당류가공품</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -20679,7 +20679,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>20220520255206</t>
+          <t>20220604079140</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20689,32 +20689,32 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>20220520255</t>
+          <t>20220604079</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>엠오에스(MOS)3</t>
+          <t>해천신골드</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>아인팜</t>
+          <t>(주)원일바이오 제1공장</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>효소식품, 청국장</t>
+          <t>칡뿌리, 맥아, 쌀겨, 황금, 삽주뿌리줄기, 맥문동뿌리, 울금덩이뿌리, 엉겅퀴, 모창출뿌리줄기, 감초, 작약뿌리, 천궁뿌리줄기, 계피, 광귤나무열매, 복령균핵, 도라지뿌리, 생강, 참당귀뿌리, 프락토올리고당, 귤나무열매껍질</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -20726,7 +20726,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>20220520255205</t>
+          <t>20220520255206</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>뿌리장</t>
+          <t>엠오에스(MOS)3</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20761,19 +20761,19 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>볶은현미, 우엉, 둥굴레, 오미자열매, 사양벌꿀, 기타가공품</t>
+          <t>효소식품, 청국장</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>202206834732011</t>
+          <t>20220520255205</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20783,22 +20783,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>20220683473</t>
+          <t>20220520255</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>매스틱 복합추출물</t>
+          <t>뿌리장</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>주식회사 에이브바이오랩스</t>
+          <t>아인팜</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -20808,19 +20808,19 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>식품첨가물, 식품첨가물, 식품첨가물혼합제제, 기타가공품, 효소식품, 식품첨가물, 식품첨가물, 식품첨가물, 기타가공품, 이눌린(고시형), 덱스트린, 식품첨가물, 식품첨가물, 혼합제제, 과.채가공품, 기타가공품, 과.채가공품</t>
+          <t>볶은현미, 우엉, 둥굴레, 오미자열매, 사양벌꿀, 기타가공품</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>202206834732013</t>
+          <t>202206834732011</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20835,7 +20835,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>젖산 마그네슘 8중 복합물</t>
+          <t>매스틱 복합추출물</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>유함유가공품, 식품첨가물, 식품첨가물, 식품첨가물, 올리고당, 포도당, 이눌린/치커리추출물(고시형), 식품첨가물, 혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 식품첨가물</t>
+          <t>식품첨가물, 식품첨가물, 식품첨가물혼합제제, 기타가공품, 효소식품, 식품첨가물, 식품첨가물, 식품첨가물, 기타가공품, 이눌린(고시형), 덱스트린, 식품첨가물, 식품첨가물, 혼합제제, 과.채가공품, 기타가공품, 과.채가공품</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -20867,7 +20867,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>202206834731993</t>
+          <t>202206834732013</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20882,7 +20882,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>조인트 밸런스 복합물</t>
+          <t>젖산 마그네슘 8중 복합물</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -20902,19 +20902,19 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>기타 수산물가공품, 기타가공품, 기타가공품, 기타 농산가공품, NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 식품첨가물, 식품첨가물혼합제제, 뮤코다당.단백(고시형), 식품첨가물, 고형차, 식품첨가물, 식품첨가물, 기타가공품, 올리고당, 식품첨가물, 덱스트린, 이눌린/치커리추출물(고시형)</t>
+          <t>유함유가공품, 식품첨가물, 식품첨가물, 식품첨가물, 올리고당, 포도당, 이눌린/치커리추출물(고시형), 식품첨가물, 혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 식품첨가물</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>202206834732023</t>
+          <t>202206834732019</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>오도미스 잇 레오 프리미엄라인</t>
+          <t>복분자 추출 복합물</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -20944,12 +20944,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>당류가공품, 식품첨가물, 이눌린/치커리추출물(고시형), 기타 농산가공품, 효소처리스테비아, 프로폴리스추출물(고시형), 기타가공품, 기타가공품, 당류가공품, 과.채가공품, 기타가공품, 기타가공품, 고형차, 기타가공품, 프로바이오틱스(고시형), 식품첨가물, 식품첨가물</t>
+          <t>이눌린/치커리추출물(고시형), 덱스트린, 식품첨가물, 기타가공품, 과.채가공품, 포도당, 식품첨가물, 고형차, 식품첨가물, 기타 식용유지가공품, 식품첨가물, 식품첨가물, 기타가공품, 식품첨가물, 기타가공품</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -20961,7 +20961,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>202206834732021</t>
+          <t>202206834731993</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20976,7 +20976,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>마가목엉겅퀴혼합추출물</t>
+          <t>조인트 밸런스 복합물</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -20991,24 +20991,24 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>기타가공품, 기타가공품</t>
+          <t>기타 수산물가공품, 기타가공품, 기타가공품, 기타 농산가공품, NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 식품첨가물, 식품첨가물혼합제제, 뮤코다당.단백(고시형), 식품첨가물, 고형차, 식품첨가물, 식품첨가물, 기타가공품, 올리고당, 식품첨가물, 덱스트린, 이눌린/치커리추출물(고시형)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>관절</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>202206834732017</t>
+          <t>202206834732007</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21023,7 +21023,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>프리미엄 젖산 마그네슘 메가 365 복합물</t>
+          <t>젖산마그네슘 밸런스 컴플렉스</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -21038,12 +21038,12 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>식품첨가물, 이눌린/치커리추출물(고시형), 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
+          <t>식품첨가물, 식품첨가물, 이눌린/치커리추출물(고시형), 당류가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -21055,7 +21055,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>202206834732019</t>
+          <t>202206834732009</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -21070,7 +21070,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>복분자 추출 복합물</t>
+          <t>매스틱 혼합추출물</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -21085,12 +21085,12 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>이눌린/치커리추출물(고시형), 덱스트린, 식품첨가물, 기타가공품, 과.채가공품, 포도당, 식품첨가물, 고형차, 식품첨가물, 기타 식용유지가공품, 식품첨가물, 식품첨가물, 기타가공품, 식품첨가물, 기타가공품</t>
+          <t>기타가공품, 과.채가공품, 혼합제제, 식품첨가물, 식품첨가물, 덱스트린, 이눌린(고시형), 기타가공품, 효소식품, 기타가공품, 과.채가공품, 식품첨가물, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -21102,7 +21102,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>202206834732007</t>
+          <t>202206834732021</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>젖산마그네슘 밸런스 컴플렉스</t>
+          <t>마가목엉겅퀴혼합추출물</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -21132,12 +21132,12 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>식품첨가물, 식품첨가물, 이눌린/치커리추출물(고시형), 당류가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
+          <t>기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -21149,7 +21149,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>202206834732009</t>
+          <t>202206834732017</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21164,7 +21164,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>매스틱 혼합추출물</t>
+          <t>프리미엄 젖산 마그네슘 메가 365 복합물</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -21179,12 +21179,12 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>기타가공품, 과.채가공품, 혼합제제, 식품첨가물, 식품첨가물, 덱스트린, 이눌린(고시형), 기타가공품, 효소식품, 기타가공품, 과.채가공품, 식품첨가물, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
+          <t>식품첨가물, 이눌린/치커리추출물(고시형), 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>202206834732015</t>
+          <t>202206834732023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>매스틱밸런스포뮬러</t>
+          <t>오도미스 잇 레오 프리미엄라인</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -21226,12 +21226,12 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>기타가공품, 효소식품, 혼합제제, 과.채가공품, 식품첨가물, 덱스트린, 포도당, 이눌린(고시형), 식품첨가물, 식품첨가물혼합제제</t>
+          <t>당류가공품, 식품첨가물, 이눌린/치커리추출물(고시형), 기타 농산가공품, 효소처리스테비아, 프로폴리스추출물(고시형), 기타가공품, 기타가공품, 당류가공품, 과.채가공품, 기타가공품, 기타가공품, 고형차, 기타가공품, 프로바이오틱스(고시형), 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -21243,7 +21243,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>202202738571325</t>
+          <t>202206834732015</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21253,12 +21253,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>20220273857</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>가득채운 복분자 정</t>
+          <t>매스틱밸런스포뮬러</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -21268,17 +21268,17 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>(주)네이처코퍼레이션</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>기타가공품, 스테아린산마그네슘</t>
+          <t>기타가공품, 효소식품, 혼합제제, 과.채가공품, 식품첨가물, 덱스트린, 포도당, 이눌린(고시형), 식품첨가물, 식품첨가물혼합제제</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -21290,7 +21290,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>202202738571324</t>
+          <t>202202738571325</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21305,12 +21305,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>발효 복분자 복합분말</t>
+          <t>가득채운 복분자 정</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -21325,19 +21325,19 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>과.채가공품, 기타가공품, 서류가공품, 과.채가공품, 기타가공품, 유산균, 비타민C, 이산화규소</t>
+          <t>기타가공품, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>20230268165166</t>
+          <t>202202738571324</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21347,12 +21347,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>20230268165</t>
+          <t>20220273857</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>G-아그작 크런치 파우더</t>
+          <t>발효 복분자 복합분말</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -21362,29 +21362,29 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>그린스퀘어(주)</t>
+          <t>(주)네이처코퍼레이션</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>곡류가공품, 곡류가공품</t>
+          <t>과.채가공품, 기타가공품, 서류가공품, 과.채가공품, 기타가공품, 유산균, 비타민C, 이산화규소</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>20230268165165</t>
+          <t>20230268165166</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21399,7 +21399,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>G-지스타 크리스피 파우더</t>
+          <t>G-아그작 크런치 파우더</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>감자플레이크, 곡류가공품</t>
+          <t>곡류가공품, 곡류가공품</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -21431,7 +21431,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>20230528144366</t>
+          <t>20230268165165</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21441,12 +21441,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20230268165</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>올인원 포뮬러 6 [콜라겐 글루타치온 히알루론산 S]</t>
+          <t>G-지스타 크리스피 파우더</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -21456,29 +21456,29 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>그린스퀘어(주)</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>비타민C, 레몬과즙분말, L-프롤린, 건조효모, 생선콜라겐분말, 자일리톨, 포도당, DL-사과산, 이산화규소, 산화아연, 효소처리스테비아, 레몬향분말, 히알루론산혼합제제, 프락토올리고당</t>
+          <t>감자플레이크, 곡류가공품</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>20230528144362</t>
+          <t>20230528144366</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>콜린 미오이노시톨 4000</t>
+          <t>올인원 포뮬러 6 [콜라겐 글루타치온 히알루론산 S]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -21513,19 +21513,19 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>건조효모(비타민D), 주석산수소콜린, α-시클로덱스트린, 유산균혼합분말, 비타민B2, 비타민B1염산염, 비타민B6염산염, 분말비타민B12혼합제제, 레몬껍질추출물분말, 자몽추출분말, 비타민E혼합제제, 구연산(무수), 효소처리스테비아, 캐롭분말, 라즈베리향분말, DL-사과산, 비타민C, 산화마그네슘, 치커리추출분말, 이노시톨</t>
+          <t>비타민C, 레몬과즙분말, L-프롤린, 건조효모, 생선콜라겐분말, 자일리톨, 포도당, DL-사과산, 이산화규소, 산화아연, 효소처리스테비아, 레몬향분말, 히알루론산혼합제제, 프락토올리고당</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>여성건강</t>
+          <t>피부</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>20230431741101</t>
+          <t>20230528144362</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21535,44 +21535,44 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>20230431741</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>수박착즙액</t>
+          <t>콜린 미오이노시톨 4000</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>(주)즙스토리</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>수박열매</t>
+          <t>건조효모(비타민D), 주석산수소콜린, α-시클로덱스트린, 유산균혼합분말, 비타민B2, 비타민B1염산염, 비타민B6염산염, 분말비타민B12혼합제제, 레몬껍질추출물분말, 자몽추출분말, 비타민E혼합제제, 구연산(무수), 효소처리스테비아, 캐롭분말, 라즈베리향분말, DL-사과산, 비타민C, 산화마그네슘, 치커리추출분말, 이노시톨</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>여성건강</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>20230609874616</t>
+          <t>20230431741101</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21582,12 +21582,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>20230609874</t>
+          <t>20230431741</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>리포좀 식물성멜라토닌 함유 멜라나잇</t>
+          <t>수박착즙액</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -21597,29 +21597,29 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>(주)뉴트리션바이오</t>
+          <t>(주)즙스토리</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>기타 농산가공품, 레몬밤분말, 기타가공품, 기타가공품, 식품첨가물, 기타 농산가공품, 기타가공품, L-트립토판, 기타가공품, 유함유가공품, 해조혼합분말, 산화마그네슘, 포도당, 과.채가공품, L-테아닌(고시형), L-시스틴, 효모식품, 효모식품</t>
+          <t>수박열매</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>20230609874615</t>
+          <t>20230609874616</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>그린 아세로라C 밸런스정</t>
+          <t>리포좀 식물성멜라토닌 함유 멜라나잇</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -21654,19 +21654,19 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>스테아린산마그네슘, 기타가공품</t>
+          <t>기타 농산가공품, 레몬밤분말, 기타가공품, 기타가공품, 식품첨가물, 기타 농산가공품, 기타가공품, L-트립토판, 기타가공품, 유함유가공품, 해조혼합분말, 산화마그네슘, 포도당, 과.채가공품, L-테아닌(고시형), L-시스틴, 효모식품, 효모식품</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>수면</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>20240661119130</t>
+          <t>20230609874615</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21676,22 +21676,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>20240661119</t>
+          <t>20230609874</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>퓨어젠 A2 양유단백질</t>
+          <t>그린 아세로라C 밸런스정</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>주식회사 뉴트리플래닛</t>
+          <t>(주)뉴트리션바이오</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -21701,19 +21701,19 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>탈지분유</t>
+          <t>스테아린산마그네슘, 기타가공품</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2024094504854</t>
+          <t>20240661119130</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21723,12 +21723,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>20240945048</t>
+          <t>20240661119</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>뿌리한입 도라지 분말유산균</t>
+          <t>퓨어젠 A2 양유단백질</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -21738,29 +21738,29 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>경남약용작물산업화지원센터</t>
+          <t>주식회사 뉴트리플래닛</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>유산균혼합분말, 도라지뿌리, 레몬과즙분말, 포도당, 레몬향분말, 구연산(무수)</t>
+          <t>탈지분유</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2024057732133</t>
+          <t>2024094504854</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21770,44 +21770,44 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>20240577321</t>
+          <t>20240945048</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>절단감자</t>
+          <t>뿌리한입 도라지 분말유산균</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>농업회사 한신식품</t>
+          <t>경남약용작물산업화지원센터</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>감자</t>
+          <t>유산균혼합분말, 도라지뿌리, 레몬과즙분말, 포도당, 레몬향분말, 구연산(무수)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>202506580412</t>
+          <t>2024057732133</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21817,32 +21817,32 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>20250658041</t>
+          <t>20240577321</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>땅콩빵쌀보리 다목적 프리믹스</t>
+          <t>절단감자</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>주식회사 세화식품</t>
+          <t>농업회사 한신식품</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>합성향료, 잔탄검, 탄산수소나트륨, 정제소금, 변성전분, 변성전분, 변성전분, 보리가루, 쌀가루, 백설탕</t>
+          <t>감자</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -21854,7 +21854,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025074252113</t>
+          <t>202506580412</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21864,44 +21864,44 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>20250742521</t>
+          <t>20250658041</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>브로멜라인 에센셜</t>
+          <t>땅콩빵쌀보리 다목적 프리믹스</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>현신바이오</t>
+          <t>주식회사 세화식품</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>유산균, 비타민미네랄혼합분말, 산화아연, 난백분, 과.채가공품, 이산화규소, 스테아린산마그네슘, 효소식품, 포도당, 케르세틴, 효소식품, 과.채가공품</t>
+          <t>합성향료, 잔탄검, 탄산수소나트륨, 정제소금, 변성전분, 변성전분, 변성전분, 보리가루, 쌀가루, 백설탕</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025074252112</t>
+          <t>2025074252113</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21916,12 +21916,12 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>AIBEL 맥주효모 비오틴</t>
+          <t>브로멜라인 에센셜</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -21931,39 +21931,39 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>두류가공품, 포도당, 효모, 스테아린산마그네슘, 판토텐산칼슘, 생선콜라겐펩타이드분말, 비타민미네랄혼합분말, 엘라스틴가수분해물, 산화아연, 니코틴산아미드, 비오틴, L-시스틴, 이산화규소</t>
+          <t>유산균, 비타민미네랄혼합분말, 산화아연, 난백분, 과.채가공품, 이산화규소, 스테아린산마그네슘, 효소식품, 포도당, 케르세틴, 효소식품, 과.채가공품</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>모발</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>19830464033570</t>
+          <t>2025074252112</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>19830464033</t>
+          <t>20250742521</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>이디야 깊고 진한 율무차</t>
+          <t>AIBEL 맥주효모 비오틴</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -21973,29 +21973,29 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>(주)오뚜기</t>
+          <t>현신바이오</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>설탕, 식물성크림, 통밀, 대두분, 아몬드, 기타가공품, 알파미분, 율무분말, 찰옥수수전분, 호두, 잣, 정제소금, 이산화규소, 땅콩향</t>
+          <t>두류가공품, 포도당, 효모, 스테아린산마그네슘, 판토텐산칼슘, 생선콜라겐펩타이드분말, 비타민미네랄혼합분말, 엘라스틴가수분해물, 산화아연, 니코틴산아미드, 비오틴, L-시스틴, 이산화규소</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>모발</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>19830464033569</t>
+          <t>19830464033570</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22010,7 +22010,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>이디야 깊고 진한 쌍화차</t>
+          <t>이디야 깊고 진한 율무차</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>정제소금, 이산화규소, 기타가공품, 덱스트린, 설탕, 대추채, 아몬드, 잣</t>
+          <t>설탕, 식물성크림, 통밀, 대두분, 아몬드, 기타가공품, 알파미분, 율무분말, 찰옥수수전분, 호두, 잣, 정제소금, 이산화규소, 땅콩향</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -22042,7 +22042,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>198604350131766</t>
+          <t>19830464033569</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22052,22 +22052,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>19860435013</t>
+          <t>19830464033</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>여에스더 리포좀 NMN 부스터</t>
+          <t>이디야 깊고 진한 쌍화차</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>캔디류</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>코스맥스바이오(주)</t>
+          <t>(주)오뚜기</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -22077,19 +22077,19 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>정제수, 알룰로오스, 에리스리톨, 로커스트콩검, 식용색소적색제40호, 니코틴산아미드, 머스켓향, 구연산, 구연산삼나트륨, 효모, 효소처리스테비아, 믹스베리향, DL-사과산, 카라기난혼합제제, 베타인, 황금추출물, 포도농축액, 베리혼합농축액, 비타민 A 혼합제제, 비타민E혼합제제, 비타민B6염산염, 비타민D3혼합제제, 비타민B12, 혼합제제</t>
+          <t>정제소금, 이산화규소, 기타가공품, 덱스트린, 설탕, 대추채, 아몬드, 잣</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>199401994801404</t>
+          <t>198604350131766</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22099,44 +22099,44 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>19940199480</t>
+          <t>19860435013</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>바닐라 분말향 #14</t>
+          <t>여에스더 리포좀 NMN 부스터</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>캔디류</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>서울향료(주)</t>
+          <t>코스맥스바이오(주)</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>포도당, 포도당, 합성향료(Vanillin)</t>
+          <t>정제수, 알룰로오스, 에리스리톨, 로커스트콩검, 식용색소적색제40호, 니코틴산아미드, 머스켓향, 구연산, 구연산삼나트륨, 효모, 효소처리스테비아, 믹스베리향, DL-사과산, 카라기난혼합제제, 베타인, 황금추출물, 포도농축액, 베리혼합농축액, 비타민 A 혼합제제, 비타민E혼합제제, 비타민B6염산염, 비타민D3혼합제제, 비타민B12, 혼합제제</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>199704451445045</t>
+          <t>199401994801404</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22146,12 +22146,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>19970445144</t>
+          <t>19940199480</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>호박카스테라크림빵용크림</t>
+          <t>바닐라 분말향 #14</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>씨제이푸드빌주식회사</t>
+          <t>서울향료(주)</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>ε-폴리리신, 기타가공품, 변성전분, 우유, 기타가공품, 난황액, 설탕, 마가린, 전분, 밀가루</t>
+          <t>포도당, 포도당, 합성향료(Vanillin)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -22183,7 +22183,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>200104450021126</t>
+          <t>199704451445045</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22193,12 +22193,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>20010445002</t>
+          <t>19970445144</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>단백질쉐이크 플레인</t>
+          <t>호박카스테라크림빵용크림</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>엠에스바이오텍(주)</t>
+          <t>씨제이푸드빌주식회사</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -22218,19 +22218,19 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>유청단백분말, L-글루타민, 효모식품, 비타민C, 기타가공품, 기타가공품, 기타가공품, 정제소금, 이산화규소, 글루콘산마그네슘, 구아검, 차전자피식이섬유(고시형), 이노시톨, 옥수수전분, L-아르지닌, L-로이신, 건조효모(크롬함유), 나한과추출물분말, 치아씨앗, 기타가공품, 난소화성말토덱스트린(고시형), 탈지분유, 향료, 두류가공품, 알룰로오스, 치커리식이섬유, 분리대두단백, 분리유단백</t>
+          <t>ε-폴리리신, 기타가공품, 변성전분, 우유, 기타가공품, 난황액, 설탕, 마가린, 전분, 밀가루</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>200303950191041</t>
+          <t>200104450021126</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22240,22 +22240,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>20030395019</t>
+          <t>20010445002</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>푸룬BCAA</t>
+          <t>단백질쉐이크 플레인</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>(주)유유헬스케어</t>
+          <t>엠에스바이오텍(주)</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -22265,19 +22265,19 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>혼합제제, 정제수, 서양자두열매착즙액</t>
+          <t>유청단백분말, L-글루타민, 효모식품, 비타민C, 기타가공품, 기타가공품, 기타가공품, 정제소금, 이산화규소, 글루콘산마그네슘, 구아검, 차전자피식이섬유(고시형), 이노시톨, 옥수수전분, L-아르지닌, L-로이신, 건조효모(크롬함유), 나한과추출물분말, 치아씨앗, 기타가공품, 난소화성말토덱스트린(고시형), 탈지분유, 향료, 두류가공품, 알룰로오스, 치커리식이섬유, 분리대두단백, 분리유단백</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>남성건강</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>200303950191039</t>
+          <t>200303950191041</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -22292,7 +22292,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>푸룬오르조젤리</t>
+          <t>푸룬BCAA</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -22312,19 +22312,19 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>혼합제제, 구연산(무수), 효소처리스테비아, 보리, 난소화성말토덱스트린(고시형), 정제수, 서양자두열매착즙액</t>
+          <t>혼합제제, 정제수, 서양자두열매착즙액</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>남성건강</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>200303950191038</t>
+          <t>200303950191039</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>키즈칼마디</t>
+          <t>푸룬오르조젤리</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -22359,19 +22359,19 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>포도향분말, 구연산(무수), 효소처리스테비아, 혼합제제, 프락토올리고당, 포도농축액분말, 유청단백분말, 산양유분말, 한속단추출분말, 초유단백분말, 비타민D3혼합제제, 글루콘산마그네슘, 구연산칼슘, 정제수</t>
+          <t>혼합제제, 구연산(무수), 효소처리스테비아, 보리, 난소화성말토덱스트린(고시형), 정제수, 서양자두열매착즙액</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>20070435069986</t>
+          <t>200303950191038</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22381,22 +22381,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>20070435069</t>
+          <t>20030395019</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>태을 순맥</t>
+          <t>키즈칼마디</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>농업법인(주)옻가네</t>
+          <t>(주)유유헬스케어</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -22406,19 +22406,19 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>정제수, 액상차</t>
+          <t>포도향분말, 구연산(무수), 효소처리스테비아, 혼합제제, 프락토올리고당, 포도농축액분말, 유청단백분말, 산양유분말, 한속단추출분말, 초유단백분말, 비타민D3혼합제제, 글루콘산마그네슘, 구연산칼슘, 정제수</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>20080415099397</t>
+          <t>20070435069986</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22428,44 +22428,44 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>20080415099</t>
+          <t>20070435069</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>휴럼 요거베리 상온발효 그릭요거트 스타터</t>
+          <t>태을 순맥</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>주식회사 휴럼</t>
+          <t>농업법인(주)옻가네</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>당류가공품, 유당, 분말결정포도당, 전지분유, 유산균, 분리유단백분말, 유산균, 유산균</t>
+          <t>정제수, 액상차</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>20080415099398</t>
+          <t>20080415099397</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>휴럼 요거베리 상온발효 카스피 그릭요거트 스타터</t>
+          <t>휴럼 요거베리 상온발효 그릭요거트 스타터</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>당류가공품, 유당, 전지분유, 분말결정포도당, 유산균, 분리유단백분말, 유산균, 치커리뿌리추출물분말, 유산균</t>
+          <t>당류가공품, 유당, 분말결정포도당, 전지분유, 유산균, 분리유단백분말, 유산균, 유산균</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -22512,7 +22512,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>20090624059790</t>
+          <t>20080415099398</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22522,22 +22522,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>20090624059</t>
+          <t>20080415099</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>석류착즙혼합액</t>
+          <t>휴럼 요거베리 상온발효 카스피 그릭요거트 스타터</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>농업회사법인(주)힐링팜</t>
+          <t>주식회사 휴럼</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -22547,19 +22547,19 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>프락토올리고당, 석류착즙액</t>
+          <t>당류가공품, 유당, 전지분유, 분말결정포도당, 유산균, 분리유단백분말, 유산균, 치커리뿌리추출물분말, 유산균</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>20100614388722</t>
+          <t>20090624059790</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22569,44 +22569,44 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>20100614388</t>
+          <t>20090624059</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>루솔 과채플랜 엘더베리&amp;양배추</t>
+          <t>석류착즙혼합액</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>(주)천호엔케어</t>
+          <t>농업회사법인(주)힐링팜</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>글루콘산아연, 효소처리스테비아, DL-사과산, 블루베리농축액, 과.채가공품, 열처리블랙엘더베리열매농축액, 사과농축액, 정제수</t>
+          <t>프락토올리고당, 석류착즙액</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>20100614388716</t>
+          <t>20100614388722</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>루솔 과채플랜 빌베리&amp;토마토</t>
+          <t>루솔 과채플랜 엘더베리&amp;양배추</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -22641,19 +22641,19 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>효소처리스테비아, 구연산(무수), 사과농축액, 정제수, 토마토농축액, 미르틸루스산앵도열매농축액, 파인애플농축액</t>
+          <t>글루콘산아연, 효소처리스테비아, DL-사과산, 블루베리농축액, 과.채가공품, 열처리블랙엘더베리열매농축액, 사과농축액, 정제수</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>201504420251392</t>
+          <t>20100614388716</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -22663,44 +22663,44 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>20150442025</t>
+          <t>20100614388</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>약도라지농축액</t>
+          <t>루솔 과채플랜 빌베리&amp;토마토</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>주식회사 하람</t>
+          <t>(주)천호엔케어</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>도라지뿌리</t>
+          <t>효소처리스테비아, 구연산(무수), 사과농축액, 정제수, 토마토농축액, 미르틸루스산앵도열매농축액, 파인애플농축액</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>20150481214138</t>
+          <t>201504420251392</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -22710,22 +22710,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>20150481214</t>
+          <t>20150442025</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>베르베린 밀크씨슬 포뮬러 MAX</t>
+          <t>약도라지농축액</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>(주)케비젠</t>
+          <t>주식회사 하람</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -22735,19 +22735,19 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>기타가공품, 스테아린산마그네슘, 기타가공품, 레드비트주스분말, 기타가공품, 기타가공품, 이노시톨, 여주추출분말, 이산화규소, 카복시메틸셀룰로스칼슘, 해조칼슘, 결정셀룰로스, 밀크씨슬추출물, 과.채가공품, 난소화성말토덱스트린(고시형)</t>
+          <t>도라지뿌리</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2016051216182</t>
+          <t>20150481214138</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -22757,22 +22757,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>20160512161</t>
+          <t>20150481214</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>나주 배도라지즙</t>
+          <t>베르베린 밀크씨슬 포뮬러 MAX</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>과.채주스</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>나주시천연색소산업화지원센터</t>
+          <t>(주)케비젠</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22782,19 +22782,19 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>도라지뿌리농축액, 배착즙액</t>
+          <t>기타가공품, 스테아린산마그네슘, 기타가공품, 레드비트주스분말, 기타가공품, 기타가공품, 이노시톨, 여주추출분말, 이산화규소, 카복시메틸셀룰로스칼슘, 해조칼슘, 결정셀룰로스, 밀크씨슬추출물, 과.채가공품, 난소화성말토덱스트린(고시형)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>20170449014375</t>
+          <t>2016051216182</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -22804,22 +22804,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>20170449014</t>
+          <t>20160512161</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>갈랑가추출분말</t>
+          <t>나주 배도라지즙</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채주스</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>(주)미전코리아</t>
+          <t>나주시천연색소산업화지원센터</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -22829,19 +22829,19 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>덱스트린, 과.채가공품</t>
+          <t>도라지뿌리농축액, 배착즙액</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>20180042370328</t>
+          <t>20170449014375</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -22851,12 +22851,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>20180042370</t>
+          <t>20170449014</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>황금 커큐민</t>
+          <t>갈랑가추출분말</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>유한네이처</t>
+          <t>(주)미전코리아</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -22876,19 +22876,19 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>정제수, 후추열매, 감귤껍질, 맥아, 마뿌리, 강황뿌리줄기</t>
+          <t>덱스트린, 과.채가공품</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>20180042928136</t>
+          <t>20180042370328</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -22898,22 +22898,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>20180042928</t>
+          <t>20180042370</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>자스민그린말차</t>
+          <t>황금 커큐민</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>액상차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>(주)우리꽃연구소</t>
+          <t>유한네이처</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22923,19 +22923,19 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>정제소금, 고형차, 효소처리스테비아, 향료, 침출차, 침출차, 정제수, 알룰로오스</t>
+          <t>정제수, 후추열매, 감귤껍질, 맥아, 마뿌리, 강황뿌리줄기</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>20190349087120</t>
+          <t>20180042928136</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -22945,22 +22945,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>20190349087</t>
+          <t>20180042928</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>본연재</t>
+          <t>자스민그린말차</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>액상차</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>투더</t>
+          <t>(주)우리꽃연구소</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>누룩, 무씨앗, 대추, 삼씨앗, 강황뿌리줄기, 감초</t>
+          <t>정제소금, 고형차, 효소처리스테비아, 향료, 침출차, 침출차, 정제수, 알룰로오스</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -22982,7 +22982,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>20190349087121</t>
+          <t>20190349087120</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>자연결</t>
+          <t>본연재</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -23017,7 +23017,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>마가목열매, 헛개나무열매, 참당귀뿌리, 천궁뿌리줄기, 뽕나무잎, 연잎</t>
+          <t>누룩, 무씨앗, 대추, 삼씨앗, 강황뿌리줄기, 감초</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -23029,7 +23029,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>201904625221243</t>
+          <t>20190349087121</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -23039,32 +23039,32 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>20190462522</t>
+          <t>20190349087</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>포도씨생강천궁복합물</t>
+          <t>자연결</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>주식회사 상상바이오</t>
+          <t>투더</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>과.채가공품, 기타가공품, 기타가공품, 과.채가공품, 설탕</t>
+          <t>마가목열매, 헛개나무열매, 참당귀뿌리, 천궁뿌리줄기, 뽕나무잎, 연잎</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -23076,7 +23076,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>201904625221242</t>
+          <t>201904625221243</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -23091,12 +23091,12 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>비타민B미네랄복합물</t>
+          <t>포도씨생강천궁복합물</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -23111,19 +23111,19 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>엽산, 판토텐산칼슘, 기타가공품, 혼합제제, 탄산마그네슘, 혼합제제, 피로인산제이철, 비타민B2, 혼합제제, 아세로라농축분말, 비타민B1염산염, 사과농축분말</t>
+          <t>과.채가공품, 기타가공품, 기타가공품, 과.채가공품, 설탕</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>항산화</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>201904625221240</t>
+          <t>201904625221242</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -23138,12 +23138,12 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>옥수수수염호박복합물</t>
+          <t>비타민B미네랄복합물</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -23153,24 +23153,24 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261010</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>옥수수수염추출분말, 옥수수수염추출분말, 설탕, 과.채가공품, 고형차, 기타가공품</t>
+          <t>엽산, 판토텐산칼슘, 기타가공품, 혼합제제, 탄산마그네슘, 혼합제제, 피로인산제이철, 비타민B2, 혼합제제, 아세로라농축분말, 비타민B1염산염, 사과농축분말</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>항산화</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2020053208585</t>
+          <t>201904625221240</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -23180,22 +23180,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>20200532085</t>
+          <t>20190462522</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>야채박사 오렌지</t>
+          <t>옥수수수염호박복합물</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>아이비씨영농조합법인</t>
+          <t>주식회사 상상바이오</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>오렌지</t>
+          <t>옥수수수염추출분말, 옥수수수염추출분말, 설탕, 과.채가공품, 고형차, 기타가공품</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -23217,7 +23217,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2020053208584</t>
+          <t>2020053208585</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -23232,7 +23232,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>야채박사 키위</t>
+          <t>야채박사 오렌지</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -23252,7 +23252,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>키위열매</t>
+          <t>오렌지</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -23264,7 +23264,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>20200363209351</t>
+          <t>2020053208584</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>20200363209</t>
+          <t>20200532085</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>딸기콩포트B</t>
+          <t>야채박사 키위</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>(주)누리지에프에스</t>
+          <t>아이비씨영농조합법인</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>키위열매</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -23311,7 +23311,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2022064807732</t>
+          <t>20200363209351</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -23321,12 +23321,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>20220648077</t>
+          <t>20200363209</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>블랙 스테비아 대추방울토마토 망고향</t>
+          <t>딸기콩포트B</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>농업회사법인 엔에프지 주식회사</t>
+          <t>(주)누리지에프에스</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>스테비올배당체, 나무토마토열매, 정제수, 수크랄로스, ε-폴리리신, 향료</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -23358,7 +23358,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2022064807733</t>
+          <t>2022064807732</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>스테비아 대추방울토마토 망고향</t>
+          <t>블랙 스테비아 대추방울토마토 망고향</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>수크랄로스, ε-폴리리신, 향료, 스테비올배당체, 정제수, 나무토마토열매</t>
+          <t>스테비올배당체, 나무토마토열매, 정제수, 수크랄로스, ε-폴리리신, 향료</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -23405,7 +23405,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>202206834732026</t>
+          <t>2022064807733</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -23415,32 +23415,32 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>20220683473</t>
+          <t>20220648077</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>프리미엄 파라다이스그레인 알파</t>
+          <t>스테비아 대추방울토마토 망고향</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>주식회사 에이브바이오랩스</t>
+          <t>농업회사법인 엔에프지 주식회사</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>이눌린/치커리추출물(고시형), 덱스트린, 식품첨가물, 과.채가공품, 두류가공품, 기타가공품, 과.채가공품, 유함유가공품, 기타 농산가공품, 식품첨가물, 식품첨가물</t>
+          <t>수크랄로스, ε-폴리리신, 향료, 스테비올배당체, 정제수, 나무토마토열매</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>202206834731912</t>
+          <t>202206834731923</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -23467,7 +23467,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>더복윤활력</t>
+          <t>키오스 매스틱 프로</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -23482,24 +23482,24 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>고형차, 고형차</t>
+          <t>고형차, 식품첨가물, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>202206834731914</t>
+          <t>202206834731912</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>마그네슘 맥스 포뮬라 99</t>
+          <t>더복윤활력</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -23529,24 +23529,24 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물</t>
+          <t>고형차, 고형차</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>202206834731920</t>
+          <t>202206834732038</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -23561,7 +23561,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>네이처엔 리포좀 비타민C 코어</t>
+          <t>소연골 콘드로이친 포뮬라 복합물</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -23576,24 +23576,24 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>식품첨가물, 고형차</t>
+          <t>식품첨가물, 기타 수산물가공품, NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 기타가공품, 기타가공품, 식품첨가물, 기타 농산가공품, 올리고당, 덱스트린, 포도당, 이눌린/치커리추출물(고시형)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>관절</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>202206834731905</t>
+          <t>202206834731914</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -23608,7 +23608,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>슈어메디 달맞이꽃종자는 처음이라</t>
+          <t>마그네슘 맥스 포뮬라 99</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -23623,12 +23623,12 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>식품첨가물, 고형차, 식품첨가물</t>
+          <t>고형차, 식품첨가물</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -23640,7 +23640,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>202206834731902</t>
+          <t>202206834731916</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -23655,7 +23655,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>더 복분자력 코어</t>
+          <t>데일리이즈 매스틱유산균밸런스</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23680,14 +23680,14 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>202206834731916</t>
+          <t>202206834732024</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>데일리이즈 매스틱유산균밸런스</t>
+          <t>마가목추출분말포뮬러</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -23717,24 +23717,24 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물</t>
+          <t>기타가공품, 덱스트린, 포도당, 기타가공품, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 식품첨가물혼합제제, 식품첨가물</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>202206834731928</t>
+          <t>202206834731881</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>철갑상어 말연골 콘드로이친 1200 MBP D3 프로</t>
+          <t>가득 채운 키오스 매스틱 정</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -23764,24 +23764,24 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>고형차, 기타가공품, 기타가공품, 기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>202206834732028</t>
+          <t>202206834731883</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>덴시녹셀 Complex</t>
+          <t>파라다이스 그레인 버닝 프라임</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -23811,12 +23811,12 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>난소화성말토덱스트린(고시형), 식품첨가물, 과.채가공품, 프로바이오틱스(고시형), 식품첨가물, 식품첨가물</t>
+          <t>고형차, 식품첨가물</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -23828,7 +23828,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>202206834732030</t>
+          <t>202206834732039</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -23843,12 +23843,12 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>매스틱추출물 포뮬러</t>
+          <t>유단백 포뮬라 MBP</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -23858,24 +23858,24 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 혼합제제, 식품첨가물, 올리고당, 난소화성말토덱스트린(고시형), 이눌린/치커리추출물(고시형), 기타가공품, 식품첨가물</t>
+          <t>유청단백분말, 유함유가공품, 유함유가공품, 식품첨가물, 고형차</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>202206834731883</t>
+          <t>202206834732026</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -23890,7 +23890,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 버닝 프라임</t>
+          <t>프리미엄 파라다이스그레인 알파</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -23905,12 +23905,12 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물</t>
+          <t>이눌린/치커리추출물(고시형), 덱스트린, 식품첨가물, 과.채가공품, 두류가공품, 기타가공품, 과.채가공품, 유함유가공품, 기타 농산가공품, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -23922,7 +23922,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>202206834731881</t>
+          <t>202206834731896</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>가득 채운 키오스 매스틱 정</t>
+          <t>셀리담 베르베린 포뮬러스</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -23952,24 +23952,24 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>식품첨가물, 고형차</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>202206834732024</t>
+          <t>202206834731909</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>마가목추출분말포뮬러</t>
+          <t>소연골콘드로이친1200 with MBP</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -23999,24 +23999,24 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>기타가공품, 덱스트린, 포도당, 기타가공품, 과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 식품첨가물혼합제제, 식품첨가물</t>
+          <t>고형차, 기타가공품</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>관절</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>202206834731918</t>
+          <t>202206834732030</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -24031,7 +24031,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>키오스 매스틱 밸런스</t>
+          <t>매스틱추출물 포뮬러</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -24046,12 +24046,12 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물</t>
+          <t>과.채가공품, 과.채가공품, 과.채가공품, 과.채가공품, 혼합제제, 식품첨가물, 올리고당, 난소화성말토덱스트린(고시형), 이눌린/치커리추출물(고시형), 기타가공품, 식품첨가물</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -24063,7 +24063,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>202206834731877</t>
+          <t>202206834731918</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -24078,7 +24078,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 버닝 정</t>
+          <t>키오스 매스틱 밸런스</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -24093,12 +24093,12 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물, 식품첨가물</t>
+          <t>고형차, 식품첨가물</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -24110,7 +24110,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>202206834732039</t>
+          <t>202206834731892</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -24125,12 +24125,12 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>유단백 포뮬라 MBP</t>
+          <t>오라엠 1000</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>당류가공품</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -24140,24 +24140,24 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>유청단백분말, 유함유가공품, 유함유가공품, 식품첨가물, 고형차</t>
+          <t>식품첨가물, 식품첨가물, 당류가공품</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>202206834731892</t>
+          <t>202206834731894</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -24172,12 +24172,12 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>오라엠 1000</t>
+          <t>슈어메디 트리플B 젖산마그네슘은 처음이라</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>당류가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -24187,12 +24187,12 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>식품첨가물, 식품첨가물, 당류가공품</t>
+          <t>고형차, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -24204,7 +24204,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>202206834731896</t>
+          <t>202206834732028</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -24219,7 +24219,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>셀리담 베르베린 포뮬러스</t>
+          <t>덴시녹셀 Complex</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -24234,24 +24234,24 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>식품첨가물, 고형차</t>
+          <t>난소화성말토덱스트린(고시형), 식품첨가물, 과.채가공품, 프로바이오틱스(고시형), 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>202206834731887</t>
+          <t>202206834731905</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>네추럴정 키오스 매스틱 유산균 알파</t>
+          <t>슈어메디 달맞이꽃종자는 처음이라</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -24281,24 +24281,24 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물</t>
+          <t>식품첨가물, 고형차, 식품첨가물</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>장건강</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>202206834731890</t>
+          <t>202206834731885</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -24313,7 +24313,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>라이젠틱 LYZENTIC</t>
+          <t>베르베린 SELECT</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -24328,24 +24328,24 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물, 식품첨가물</t>
+          <t>고형차, 식품첨가물</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>202206834731894</t>
+          <t>202206834731902</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>슈어메디 트리플B 젖산마그네슘은 처음이라</t>
+          <t>더 복분자력 코어</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -24375,12 +24375,12 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물, 식품첨가물</t>
+          <t>고형차, 식품첨가물</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>202206834731900</t>
+          <t>202206834731928</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -24407,7 +24407,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>플러스 키오스 매스틱</t>
+          <t>철갑상어 말연골 콘드로이친 1200 MBP D3 프로</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -24422,24 +24422,24 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>식품첨가물, 고형차</t>
+          <t>고형차, 기타가공품, 기타가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>관절</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>202206834731898</t>
+          <t>202206834731920</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>베르베린</t>
+          <t>네이처엔 리포좀 비타민C 코어</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -24469,24 +24469,24 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물</t>
+          <t>식품첨가물, 고형차</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>202206834731923</t>
+          <t>202206834731877</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -24501,7 +24501,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>키오스 매스틱 프로</t>
+          <t>파라다이스 그레인 버닝 정</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -24516,12 +24516,12 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물, 식품첨가물, 식품첨가물</t>
+          <t>고형차, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -24533,7 +24533,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>202206834732038</t>
+          <t>202206834731890</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>소연골 콘드로이친 포뮬라 복합물</t>
+          <t>라이젠틱 LYZENTIC</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -24563,24 +24563,24 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>식품첨가물, 기타 수산물가공품, NAG(엔에이지, N-아세틸글루코사민, N-Acetylglucosamine)(고시형), 기타가공품, 기타가공품, 식품첨가물, 기타 농산가공품, 올리고당, 덱스트린, 포도당, 이눌린/치커리추출물(고시형)</t>
+          <t>고형차, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>202206834731875</t>
+          <t>202206834731887</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -24595,7 +24595,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>이너도르 데오잇</t>
+          <t>네추럴정 키오스 매스틱 유산균 알파</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -24610,17 +24610,17 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>이눌린/치커리추출물(고시형), 덱스트린, 과.채가공품, 기타가공품, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 기타가공품, 식품첨가물</t>
+          <t>고형차, 식품첨가물</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>장건강</t>
         </is>
       </c>
     </row>
@@ -24657,7 +24657,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -24674,7 +24674,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>202206834731909</t>
+          <t>202206834732032</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -24689,7 +24689,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>소연골콘드로이친1200 with MBP</t>
+          <t>트리플마그네슘믹스</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -24704,24 +24704,24 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>고형차, 기타가공품</t>
+          <t>이눌린/치커리추출물(고시형), 덱스트린, 당류가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 유함유가공품, 식품첨가물, 식품첨가물</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>관절</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>202206834732032</t>
+          <t>202206834731875</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -24736,7 +24736,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>트리플마그네슘믹스</t>
+          <t>이너도르 데오잇</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -24751,12 +24751,12 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>이눌린/치커리추출물(고시형), 덱스트린, 당류가공품, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 식품첨가물, 식품첨가물, 식품첨가물, 유함유가공품, 식품첨가물, 식품첨가물</t>
+          <t>이눌린/치커리추출물(고시형), 덱스트린, 과.채가공품, 기타가공품, 식품첨가물, 식품첨가물, 식품첨가물혼합제제, 기타가공품, 식품첨가물</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -24768,7 +24768,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>202206834731885</t>
+          <t>202206834731900</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -24783,7 +24783,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>베르베린 SELECT</t>
+          <t>플러스 키오스 매스틱</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -24798,24 +24798,24 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물</t>
+          <t>식품첨가물, 고형차</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>혈당</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>202202738571327</t>
+          <t>202206834731898</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -24825,12 +24825,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>20220273857</t>
+          <t>20220683473</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>파라다이스 그레인 버닝 마스터</t>
+          <t>베르베린</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -24840,29 +24840,29 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>(주)네이처코퍼레이션</t>
+          <t>주식회사 에이브바이오랩스</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>기타가공품, 스테아린산마그네슘</t>
+          <t>고형차, 식품첨가물</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>혈당</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>202202738571326</t>
+          <t>202202738571327</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -24877,12 +24877,12 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>뉴 파라다이스 그레인 분말</t>
+          <t>파라다이스 그레인 버닝 마스터</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>고형차</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -24897,19 +24897,19 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>기타가공품, 과.채가공품, 이산화규소, 효소식품, α-시클로덱스트린, 기타가공품, 기타가공품, 기타가공품, 포도당, 기타 농산가공품, 기타가공품</t>
+          <t>기타가공품, 스테아린산마그네슘</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>다이어트</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>20230528144369</t>
+          <t>202202738571326</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -24919,12 +24919,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>20230528144</t>
+          <t>20220273857</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>쌀 발효 양태반 플라센타 프라임</t>
+          <t>뉴 파라다이스 그레인 분말</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -24934,29 +24934,29 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>바이오디피씨(주)</t>
+          <t>(주)네이처코퍼레이션</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>기타가공품, 과.채가공품, 이산화규소, 효소식품, α-시클로덱스트린, 기타가공품, 기타가공품, 기타가공품, 포도당, 기타 농산가공품, 기타가공품</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>다이어트</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>20230528144368</t>
+          <t>20230528144369</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>쌀 발효 양태반 복합물</t>
+          <t>쌀 발효 양태반 플라센타 프라임</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -24991,19 +24991,19 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>구연산(무수), 오렌지맛분말, 드링크향, 오렌지과즙분말, 파인애플맛분말, 양태반분말, 파인애플주스분말, 자일리톨, 포도당, L-시스틴, L-아르지닌, 쌀발효분말, DL-사과산, 이산화규소, 녹용분말, 침향나무수지가침착된수간목분말, 영지버섯자실체추출분말, 산화아연, 비타민B6염산염, 비타민B2, 비타민B1염산염</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>20230528144367</t>
+          <t>20230528144368</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>파워 마그네슘</t>
+          <t>쌀 발효 양태반 복합물</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -25038,19 +25038,19 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>파인애플향분말, 파인애플농축, 글루콘산마그네슘, 자일리톨, 포도당, DL-사과산, 효소처리스테비아, L-젖산마그네슘, 구연산(무수), 이산화규소, 파인애플맛분말</t>
+          <t>구연산(무수), 오렌지맛분말, 드링크향, 오렌지과즙분말, 파인애플맛분말, 양태반분말, 파인애플주스분말, 자일리톨, 포도당, L-시스틴, L-아르지닌, 쌀발효분말, DL-사과산, 이산화규소, 녹용분말, 침향나무수지가침착된수간목분말, 영지버섯자실체추출분말, 산화아연, 비타민B6염산염, 비타민B2, 비타민B1염산염</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>에너지</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>20230612332357</t>
+          <t>20230528144367</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -25060,12 +25060,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>20230612332</t>
+          <t>20230528144</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>꽃송이칸</t>
+          <t>파워 마그네슘</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -25075,17 +25075,17 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>(주)웰레스트</t>
+          <t>바이오디피씨(주)</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>꽃송이버섯분말, 덱스트린, 치커리뿌리추출물분말, 곡류가공품, 귀리식이섬유, 병풀추출, 볶은현미, 고형차, 효모식품, 대나무수액, 인절미향</t>
+          <t>파인애플향분말, 파인애플농축, 글루콘산마그네슘, 자일리톨, 포도당, DL-사과산, 효소처리스테비아, L-젖산마그네슘, 구연산(무수), 이산화규소, 파인애플맛분말</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -25097,7 +25097,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2023080138111</t>
+          <t>20230612332357</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -25107,12 +25107,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>20230801381</t>
+          <t>20230612332</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>셀로커브</t>
+          <t>꽃송이칸</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>영농조합법인 금강농산</t>
+          <t>(주)웰레스트</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>건조팽이버섯분말, 구아검가수분해물(고시형), 트레할로스, 이눌린분말, 난소화성말토덱스트린분말(고시형)</t>
+          <t>꽃송이버섯분말, 덱스트린, 치커리뿌리추출물분말, 곡류가공품, 귀리식이섬유, 병풀추출, 볶은현미, 고형차, 효모식품, 대나무수액, 인절미향</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -25144,7 +25144,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>202605853077</t>
+          <t>2023080138111</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -25154,12 +25154,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>20260585307</t>
+          <t>20230801381</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>꿀요거트볼</t>
+          <t>셀로커브</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -25169,7 +25169,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>우리웰푸드 농업회사법인 주식회사</t>
+          <t>영농조합법인 금강농산</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -25179,7 +25179,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>농후발효유, 사양벌꿀</t>
+          <t>건조팽이버섯분말, 구아검가수분해물(고시형), 트레할로스, 이눌린분말, 난소화성말토덱스트린분말(고시형)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -25191,22 +25191,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>200204150291269</t>
+          <t>202605853077</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>20020415029</t>
+          <t>20260585307</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>황성주 박사의 1일 1프로틴 블랙</t>
+          <t>꿀요거트볼</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -25216,29 +25216,29 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>(주)엄마사랑</t>
+          <t>우리웰푸드 농업회사법인 주식회사</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>효소식품, 식품첨가물혼합제제, 니코틴산아미드, 산화아연, 판토텐산칼슘, 식품첨가물혼합제제, 기타가공품, 두류가공품, 두류가공품, 난소화성말토덱스트린분말(고시형), 곡류가공품, 현미, 곡류가공품, 두류가공품, 에리스리톨, 두류가공품, 분리대두단백, 생식제품, 식품첨가물혼합제제, 효소처리스테비아, 저분자콜라겐펩타이드(기능성원료인정제2013-30호)</t>
+          <t>농후발효유, 사양벌꿀</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>단백질</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>201504420251393</t>
+          <t>200204150291269</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -25248,44 +25248,44 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>20150442025</t>
+          <t>20020415029</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>도라지농축액HR-5564</t>
+          <t>황성주 박사의 1일 1프로틴 블랙</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>과.채가공품</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>주식회사 하람</t>
+          <t>(주)엄마사랑</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>정제수, 도라지뿌리</t>
+          <t>효소식품, 식품첨가물혼합제제, 니코틴산아미드, 산화아연, 판토텐산칼슘, 식품첨가물혼합제제, 기타가공품, 두류가공품, 두류가공품, 난소화성말토덱스트린분말(고시형), 곡류가공품, 현미, 곡류가공품, 두류가공품, 에리스리톨, 두류가공품, 분리대두단백, 생식제품, 식품첨가물혼합제제, 효소처리스테비아, 저분자콜라겐펩타이드(기능성원료인정제2013-30호)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>20200424149192</t>
+          <t>201504420251393</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -25295,44 +25295,44 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>20200424149</t>
+          <t>20150442025</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>돈태반발효추출액</t>
+          <t>도라지농축액HR-5564</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>기타가공품</t>
+          <t>과.채가공품</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>(주)네츄럴굿띵스</t>
+          <t>주식회사 하람</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>기타가공품, Bacillus amyloliquefaciens, 정제수</t>
+          <t>정제수, 도라지뿌리</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>면역</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>202206834731941</t>
+          <t>20200195385104</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -25342,44 +25342,44 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>20220683473</t>
+          <t>20200195385</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>파이토 삼백초 맥문동 99 맥스정</t>
+          <t>서리태프로틴바 흑임자맛</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>고형차</t>
+          <t>기타가공품</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>주식회사 에이브바이오랩스</t>
+          <t>주식회사베노프하우스</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>고형차, 식품첨가물</t>
+          <t>기타가공품, 프락토올리고당, 두류가공품, 당류가공품, 두류가공품, 두류가공품, 두류가공품, 폴리덱스트로스, 당류가공품, 현미유, 물엿, 기타가공품, 기타소금, 효소처리스테비아, 아라비아검, 정제수, 레시틴, 글리세린, 난소화성말토덱스트린분말(고시형)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>면역</t>
+          <t>단백질</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2023058606616</t>
+          <t>20200195385103</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -25389,12 +25389,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>20230586066</t>
+          <t>20200195385</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>해바라기유분말</t>
+          <t>서리태프로틴바 서리태인절미맛</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -25404,17 +25404,17 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>유니바이오팜</t>
+          <t>주식회사베노프하우스</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>비타민C, d-토코페롤(혼합형), 레시틴(고시형), 제삼인산나트륨, 글리세린지방산에스테르, 유청단백분말, 해바라기유, 물엿</t>
+          <t>기타가공품, 기타소금, 효소처리스테비아, 아라비아검, 정제수, 레시틴, 글리세린, 난소화성말토덱스트린분말(고시형), 프락토올리고당, 현미유, 물엿, 볶은콩가루, 당류가공품, 두류가공품, 당류가공품, 두류가공품, 두류가공품, 두류가공품, 폴리덱스트로스</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -25426,45 +25426,233 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
+          <t>20200424149192</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>20200424149</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>돈태반발효추출액</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>(주)네츄럴굿띵스</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>20261011</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>기타가공품, Bacillus amyloliquefaciens, 정제수</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>202206834731941</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>20220683473</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>파이토 삼백초 맥문동 99 맥스정</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>고형차</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>주식회사 에이브바이오랩스</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>20261011</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>고형차, 식품첨가물</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>면역</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>20220820077182</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>20220820077</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>유기농 레드와인비니거 복합분말</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>당류가공품</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>주식회사 에이원바이옴</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>20261011</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>기타가공품, 포도당</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2023058606616</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>20230586066</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>해바라기유분말</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>기타가공품</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>유니바이오팜</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>20261011</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>비타민C, d-토코페롤(혼합형), 레시틴(고시형), 제삼인산나트륨, 글리세린지방산에스테르, 유청단백분말, 해바라기유, 물엿</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>단백질</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
           <t>20230609874620</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B356" t="inlineStr">
         <is>
           <t>20261008</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C356" t="inlineStr">
         <is>
           <t>20230609874</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
+      <c r="D356" t="inlineStr">
         <is>
           <t>프리미엄 참좋은 크랜베리</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
+      <c r="E356" t="inlineStr">
         <is>
           <t>과.채가공품</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
+      <c r="F356" t="inlineStr">
         <is>
           <t>(주)뉴트리션바이오</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr">
+      <c r="G356" t="inlineStr">
         <is>
           <t>20261009</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
+      <c r="H356" t="inlineStr">
         <is>
           <t>기타가공품, 스테아린산마그네슘, 이산화규소, 산화아연, D-만노오스, 비타민B6염산염, 과.채가공품, 과.채가공품, 과.채가공품</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr">
+      <c r="I356" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
@@ -28668,7 +28856,7 @@
         <v>19</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>1</v>
@@ -28710,13 +28898,13 @@
         <v>3</v>
       </c>
       <c r="R47" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S47" s="10" t="n">
         <v>214</v>
       </c>
       <c r="T47" s="8" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48">
@@ -28732,7 +28920,7 @@
         <v>-37</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>-61</v>
+        <v>-59</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>-33</v>
@@ -28774,13 +28962,13 @@
         <v>-9</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>-53</v>
+        <v>-51</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>-798</v>
       </c>
       <c r="T48" s="12" t="n">
-        <v>-1265</v>
+        <v>-1261</v>
       </c>
     </row>
     <row r="49">
@@ -28860,7 +29048,7 @@
         <v>-19</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>-1</v>
@@ -28902,13 +29090,13 @@
         <v>-3</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>-214</v>
       </c>
       <c r="T50" s="12" t="n">
-        <v>-351</v>
+        <v>-355</v>
       </c>
     </row>
     <row r="51">
